--- a/2D 자동 제작도 개발 현황.xlsx
+++ b/2D 자동 제작도 개발 현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F187E248-2EF2-4954-B040-2A45F3210D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC6A772-55AC-4F2B-A523-AE28161FEB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="489">
   <si>
     <t>2D 자동 제작도 개발 현황</t>
   </si>
@@ -1048,12 +1048,6 @@
     <t>고정 열 너비 + 폰트 축소</t>
   </si>
   <si>
-    <t>앱/템플릿 조정</t>
-  </si>
-  <si>
-    <t>SPREF 실제 샘플과 표준 약어 결정 필요</t>
-  </si>
-  <si>
     <t>조립도</t>
   </si>
   <si>
@@ -1493,6 +1487,26 @@
   </si>
   <si>
     <t>낮은 우선순위이며 아직 요청 미전달</t>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOM 텍스트 줄바꿈·열 너비 실기 확인 완료</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1902,7 +1916,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1933,17 +1947,44 @@
     <xf numFmtId="176" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1987,13 +2028,16 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2031,42 +2075,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2603,28 +2611,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3"/>
@@ -2635,54 +2643,54 @@
       <c r="F3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="27"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="18">
+      <c r="A5" s="27">
         <f>COUNTA('개발 항목'!$D$6:$D$79)</f>
         <v>74</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="18">
+      <c r="B5" s="28"/>
+      <c r="C5" s="27">
         <f>COUNTIF('개발 항목'!$I$6:$I$79,"완료")</f>
-        <v>27</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="18">
+        <v>28</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="27">
         <f>COUNTIF('개발 항목'!$I$6:$I$79,"실기 검증 대기")</f>
         <v>10</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="18">
+      <c r="F5" s="28"/>
+      <c r="G5" s="27">
         <f>COUNTIFS('개발 항목'!$E$6:$E$79,"○",'개발 항목'!$H$6:$H$79,"&lt;&gt;O")</f>
         <v>35</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7"/>
@@ -2693,16 +2701,16 @@
       <c r="F7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
@@ -2973,89 +2981,96 @@
       <c r="F19"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:B4"/>
@@ -3066,13 +3081,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H6"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B21:H21"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3092,7 +3100,7 @@
     <col min="6" max="6" width="13.19921875" style="5" customWidth="1"/>
     <col min="7" max="7" width="15" style="5" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="53" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="16" customWidth="1"/>
     <col min="10" max="10" width="37" style="5" customWidth="1"/>
     <col min="11" max="11" width="17.19921875" style="5" customWidth="1"/>
     <col min="12" max="13" width="13.69921875" customWidth="1"/>
@@ -3103,70 +3111,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
     </row>
     <row r="5" spans="1:18" ht="43.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
@@ -3233,7 +3241,7 @@
         <v>207</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>76</v>
@@ -3251,10 +3259,10 @@
         <v>162</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>54</v>
@@ -3270,7 +3278,7 @@
         <v>46225</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="R6"/>
     </row>
@@ -3279,13 +3287,13 @@
         <v>51</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>292</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>55</v>
@@ -3300,10 +3308,10 @@
         <v>246</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>79</v>
@@ -3322,7 +3330,7 @@
         <v>46226</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="R7"/>
     </row>
@@ -3547,13 +3555,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>76</v>
@@ -3571,7 +3579,7 @@
         <v>2</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>79</v>
@@ -3592,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="R12"/>
     </row>
@@ -3601,13 +3609,13 @@
         <v>16</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>76</v>
@@ -3625,7 +3633,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>79</v>
@@ -3646,7 +3654,7 @@
         <v>46225</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="R13"/>
     </row>
@@ -3661,7 +3669,7 @@
         <v>249</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>76</v>
@@ -3679,7 +3687,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>79</v>
@@ -3698,7 +3706,7 @@
         <v>46224</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R14"/>
     </row>
@@ -3713,7 +3721,7 @@
         <v>190</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>113</v>
@@ -3731,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>79</v>
@@ -3750,7 +3758,7 @@
         <v>46156</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="R15"/>
     </row>
@@ -3762,7 +3770,7 @@
         <v>212</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>141</v>
@@ -3783,7 +3791,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>79</v>
@@ -3804,7 +3812,7 @@
         <v>46224</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="R16"/>
     </row>
@@ -3816,10 +3824,10 @@
         <v>212</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>55</v>
@@ -3837,7 +3845,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>79</v>
@@ -3858,7 +3866,7 @@
         <v>46225</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="R17"/>
     </row>
@@ -3870,10 +3878,10 @@
         <v>212</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>55</v>
@@ -3891,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>79</v>
@@ -3910,7 +3918,7 @@
         <v>46223</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="R18"/>
     </row>
@@ -3925,7 +3933,7 @@
         <v>249</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>76</v>
@@ -3943,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>79</v>
@@ -3962,7 +3970,7 @@
         <v>46156</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R19"/>
     </row>
@@ -3977,7 +3985,7 @@
         <v>249</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>76</v>
@@ -3995,7 +4003,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>79</v>
@@ -4014,7 +4022,7 @@
         <v>46156</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R20"/>
     </row>
@@ -4029,7 +4037,7 @@
         <v>249</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>76</v>
@@ -4047,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>79</v>
@@ -4066,7 +4074,7 @@
         <v>46156</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R21"/>
     </row>
@@ -4078,10 +4086,10 @@
         <v>240</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>76</v>
@@ -4099,7 +4107,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>79</v>
@@ -4118,7 +4126,7 @@
         <v>46156</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="R22"/>
     </row>
@@ -4133,7 +4141,7 @@
         <v>185</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>76</v>
@@ -4151,7 +4159,7 @@
         <v>2</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>79</v>
@@ -4170,7 +4178,7 @@
         <v>46225</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R23"/>
     </row>
@@ -4203,7 +4211,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>79</v>
@@ -4222,7 +4230,7 @@
         <v>46156</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R24"/>
     </row>
@@ -4237,7 +4245,7 @@
         <v>185</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>76</v>
@@ -4255,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>79</v>
@@ -4276,7 +4284,7 @@
         <v>46226</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="R25"/>
     </row>
@@ -4309,7 +4317,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>79</v>
@@ -4361,7 +4369,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>79</v>
@@ -4380,7 +4388,7 @@
         <v>46224</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R27"/>
     </row>
@@ -4389,13 +4397,13 @@
         <v>31</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>76</v>
@@ -4413,7 +4421,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>79</v>
@@ -4434,7 +4442,7 @@
         <v>46225</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="R28"/>
     </row>
@@ -4443,13 +4451,13 @@
         <v>49</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>292</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>76</v>
@@ -4467,7 +4475,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>79</v>
@@ -4488,7 +4496,7 @@
         <v>46224</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="R29"/>
     </row>
@@ -4503,7 +4511,7 @@
         <v>292</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>76</v>
@@ -4521,7 +4529,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>79</v>
@@ -4542,7 +4550,7 @@
         <v>46224</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="R30"/>
     </row>
@@ -4554,10 +4562,10 @@
         <v>171</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>55</v>
@@ -4575,7 +4583,7 @@
         <v>2</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>79</v>
@@ -4596,7 +4604,7 @@
         <v>46222</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="R31"/>
     </row>
@@ -4608,10 +4616,10 @@
         <v>171</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>55</v>
@@ -4629,7 +4637,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>79</v>
@@ -4650,7 +4658,7 @@
         <v>46225</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="R32"/>
     </row>
@@ -4662,10 +4670,10 @@
         <v>240</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>55</v>
@@ -4683,7 +4691,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>79</v>
@@ -4704,61 +4712,61 @@
         <v>46225</v>
       </c>
       <c r="Q33" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="10">
+        <v>69</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="R33"/>
-    </row>
-    <row r="34" spans="1:18" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="43">
-        <v>69</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="C34" s="43" t="s">
+      <c r="E34" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J34" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="K34" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="13">
+        <v>46225</v>
+      </c>
+      <c r="O34" s="13">
+        <v>46225</v>
+      </c>
+      <c r="P34" s="13">
+        <v>46225</v>
+      </c>
+      <c r="Q34" s="10" t="s">
         <v>457</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="H34" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="I34" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="J34" s="43" t="s">
-        <v>458</v>
-      </c>
-      <c r="K34" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="L34" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="M34" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="46">
-        <v>46225</v>
-      </c>
-      <c r="O34" s="46">
-        <v>46225</v>
-      </c>
-      <c r="P34" s="46">
-        <v>46225</v>
-      </c>
-      <c r="Q34" s="43" t="s">
-        <v>459</v>
       </c>
       <c r="R34"/>
     </row>
@@ -4926,10 +4934,10 @@
         <v>166</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>76</v>
@@ -4947,7 +4955,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>79</v>
@@ -4966,7 +4974,7 @@
         <v>46224</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="R38"/>
     </row>
@@ -4975,13 +4983,13 @@
         <v>18</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>76</v>
@@ -4999,7 +5007,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>79</v>
@@ -5018,7 +5026,7 @@
         <v>46224</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="R39"/>
     </row>
@@ -5033,7 +5041,7 @@
         <v>292</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>76</v>
@@ -5051,7 +5059,7 @@
         <v>3</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>79</v>
@@ -5070,7 +5078,7 @@
         <v>46225</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="R40"/>
     </row>
@@ -5085,7 +5093,7 @@
         <v>297</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>76</v>
@@ -5103,7 +5111,7 @@
         <v>3</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>79</v>
@@ -5122,7 +5130,7 @@
         <v>46225</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="R41"/>
     </row>
@@ -5137,7 +5145,7 @@
         <v>297</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>76</v>
@@ -5155,7 +5163,7 @@
         <v>3</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>79</v>
@@ -5174,7 +5182,7 @@
         <v>46225</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="R42"/>
     </row>
@@ -5186,10 +5194,10 @@
         <v>160</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>76</v>
@@ -5207,7 +5215,7 @@
         <v>3</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>304</v>
@@ -5226,7 +5234,7 @@
         <v>46225</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="R43"/>
     </row>
@@ -5238,10 +5246,10 @@
         <v>160</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>55</v>
@@ -5259,7 +5267,7 @@
         <v>3</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>79</v>
@@ -5278,7 +5286,7 @@
         <v>46225</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="R44"/>
     </row>
@@ -5443,7 +5451,7 @@
         <v>190</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>113</v>
@@ -5478,7 +5486,7 @@
         <v>46225</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R48"/>
     </row>
@@ -5490,10 +5498,10 @@
         <v>171</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>55</v>
@@ -5511,10 +5519,10 @@
         <v>114</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>54</v>
@@ -5530,7 +5538,7 @@
         <v>46225</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R49"/>
     </row>
@@ -5542,10 +5550,10 @@
         <v>160</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>55</v>
@@ -5563,7 +5571,7 @@
         <v>114</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>210</v>
@@ -5580,7 +5588,7 @@
         <v>46224</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R50"/>
     </row>
@@ -6022,22 +6030,22 @@
         <v>76</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>113</v>
+        <v>484</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>273</v>
+        <v>484</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>85</v>
+        <v>485</v>
       </c>
       <c r="J59" s="7" t="s">
         <v>336</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>337</v>
+        <v>486</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>54</v>
+        <v>487</v>
       </c>
       <c r="M59" s="8" t="s">
         <v>55</v>
@@ -6045,12 +6053,14 @@
       <c r="N59" s="9">
         <v>46152</v>
       </c>
-      <c r="O59" s="9"/>
+      <c r="O59" s="9">
+        <v>46226</v>
+      </c>
       <c r="P59" s="9">
-        <v>46155</v>
+        <v>46226</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>338</v>
+        <v>488</v>
       </c>
       <c r="R59"/>
     </row>
@@ -6062,10 +6072,10 @@
         <v>240</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>55</v>
@@ -6083,10 +6093,10 @@
         <v>85</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>54</v>
@@ -6102,7 +6112,7 @@
         <v>46225</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="R60"/>
     </row>
@@ -6674,10 +6684,10 @@
         <v>220</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>55</v>
@@ -6692,13 +6702,13 @@
         <v>246</v>
       </c>
       <c r="I72" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="K72" s="8" t="s">
         <v>407</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="K72" s="8" t="s">
-        <v>409</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>55</v>
@@ -6712,7 +6722,7 @@
         <v>46225</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="R72"/>
     </row>
@@ -6921,152 +6931,152 @@
       </c>
     </row>
     <row r="77" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="44">
+      <c r="A77" s="11">
         <v>32</v>
       </c>
-      <c r="B77" s="44" t="s">
+      <c r="B77" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="44" t="s">
+      <c r="C77" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E77" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="F77" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="G77" s="44" t="s">
+      <c r="E77" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="H77" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="I77" s="44" t="s">
+      <c r="H77" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="J77" s="45" t="s">
+      <c r="J77" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="K77" s="44" t="s">
+      <c r="K77" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="L77" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="M77" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="N77" s="47">
+      <c r="L77" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N77" s="14">
         <v>46224</v>
       </c>
-      <c r="O77" s="47"/>
-      <c r="P77" s="47">
+      <c r="O77" s="14"/>
+      <c r="P77" s="14">
         <v>46225</v>
       </c>
-      <c r="Q77" s="45" t="s">
+      <c r="Q77" s="12" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="48">
+      <c r="A78">
         <v>70</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B78" t="s">
         <v>212</v>
       </c>
-      <c r="C78" s="48" t="s">
+      <c r="C78" t="s">
         <v>330</v>
       </c>
-      <c r="D78" s="48" t="s">
+      <c r="D78" t="s">
+        <v>458</v>
+      </c>
+      <c r="E78" t="s">
+        <v>76</v>
+      </c>
+      <c r="F78" t="s">
+        <v>55</v>
+      </c>
+      <c r="G78" t="s">
+        <v>55</v>
+      </c>
+      <c r="H78" t="s">
+        <v>55</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J78" t="s">
+        <v>459</v>
+      </c>
+      <c r="K78" t="s">
+        <v>252</v>
+      </c>
+      <c r="L78" t="s">
+        <v>54</v>
+      </c>
+      <c r="M78" t="s">
+        <v>54</v>
+      </c>
+      <c r="N78" s="15"/>
+      <c r="O78" s="15"/>
+      <c r="P78" s="15">
+        <v>46225</v>
+      </c>
+      <c r="Q78" t="s">
         <v>460</v>
       </c>
-      <c r="E78" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="F78" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="G78" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="H78" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="I78" s="54" t="s">
+    </row>
+    <row r="79" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>71</v>
+      </c>
+      <c r="B79" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" t="s">
+        <v>330</v>
+      </c>
+      <c r="D79" t="s">
+        <v>461</v>
+      </c>
+      <c r="E79" t="s">
+        <v>55</v>
+      </c>
+      <c r="F79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s">
+        <v>55</v>
+      </c>
+      <c r="H79" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="J78" s="48" t="s">
-        <v>461</v>
-      </c>
-      <c r="K78" s="48" t="s">
-        <v>252</v>
-      </c>
-      <c r="L78" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="M78" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="N78" s="49"/>
-      <c r="O78" s="49"/>
-      <c r="P78" s="49">
+      <c r="J79" t="s">
+        <v>462</v>
+      </c>
+      <c r="K79" t="s">
+        <v>257</v>
+      </c>
+      <c r="L79" t="s">
+        <v>55</v>
+      </c>
+      <c r="M79" t="s">
+        <v>54</v>
+      </c>
+      <c r="N79" s="15"/>
+      <c r="O79" s="15"/>
+      <c r="P79" s="15">
         <v>46225</v>
       </c>
-      <c r="Q78" s="48" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="48">
-        <v>71</v>
-      </c>
-      <c r="B79" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="C79" s="48" t="s">
-        <v>330</v>
-      </c>
-      <c r="D79" s="48" t="s">
+      <c r="Q79" t="s">
         <v>463</v>
-      </c>
-      <c r="E79" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="F79" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="G79" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="H79" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="I79" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="J79" s="48" t="s">
-        <v>464</v>
-      </c>
-      <c r="K79" s="48" t="s">
-        <v>257</v>
-      </c>
-      <c r="L79" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="M79" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="N79" s="49"/>
-      <c r="O79" s="49"/>
-      <c r="P79" s="49">
-        <v>46225</v>
-      </c>
-      <c r="Q79" s="48" t="s">
-        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -7200,37 +7210,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
@@ -7348,15 +7358,15 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
@@ -7406,7 +7416,7 @@
     </row>
     <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>76</v>
@@ -7415,16 +7425,16 @@
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -7566,15 +7576,15 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
     </row>
     <row r="23" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
@@ -7601,7 +7611,7 @@
     </row>
     <row r="24" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>76</v>
@@ -7610,16 +7620,16 @@
         <v>192</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -7853,15 +7863,15 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
     </row>
     <row r="37" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
@@ -7911,16 +7921,16 @@
     </row>
     <row r="39" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>79</v>
@@ -7929,12 +7939,12 @@
         <v>79</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>55</v>
@@ -7943,7 +7953,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>79</v>
@@ -7952,12 +7962,12 @@
         <v>79</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>76</v>
@@ -7966,7 +7976,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>79</v>
@@ -7975,64 +7985,64 @@
         <v>79</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
+        <v>480</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>405</v>
+      </c>
+      <c r="D42" t="s">
+        <v>481</v>
+      </c>
+      <c r="E42" t="s">
         <v>482</v>
       </c>
-      <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>407</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>483</v>
       </c>
-      <c r="E42" t="s">
-        <v>484</v>
-      </c>
-      <c r="F42" t="s">
-        <v>409</v>
-      </c>
-      <c r="G42" t="s">
-        <v>485</v>
-      </c>
     </row>
     <row r="43" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="34"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="44"/>
     </row>
     <row r="44" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="37"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="47"/>
     </row>
     <row r="45" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="40"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/2D 자동 제작도 개발 현황.xlsx
+++ b/2D 자동 제작도 개발 현황.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="Rc102e897654c4001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="Rf1ba8e6b5a2943ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="R7fecffbeb8794ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="R874dc58789534ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="R8c58ec05fc2f4eb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="R7e6bf996d9414ec2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,6 +57,138 @@
     <x:t xml:space="preserve">최근 변경</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">가공도</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">첫 2D 캡처 AccessViolation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">출력 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가공도·4종 일괄 차단</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API 요청 전달 후 수정본 재검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가공도 캡처 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">설치도</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">기준 Part 끝단→연결 Part 접합측 모서리 치수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">설치 위치 정보 신뢰성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대표 STRU PDF로 실제 끝단·모서리 검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">설치도 PreparedDimensions</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">공통</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2D 모서리·홀·실선/은선 누락</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API 대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">형상 누락</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-07-23 API 배포분으로 재검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">형상·은선 렌더</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EA 축척·풍선·은선</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가공 치수·표현</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">신 DLL 적용 후 EA 실기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EA 렌더·SDK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Q'TY·MA·FA 실제 데이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">개발 필요</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BOM 생산정보 오류</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UDA/집계 규칙 확정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">현재 임시값</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">표제부</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Paint Code(PNT)·DP No·Note·Rev</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">개발 대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">생산/문서정보 누락</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PNT→Input 165 구현과 입력 데이터 확정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PNT UDA·템플릿 자리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">기울어진 부재·라운드·모떼기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">분석 필요</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">치수·형상 표현</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">적용 범위와 필터 조건 확정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">형상·치수 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">최종</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">제작·가공·설치도 최종 생산 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">부분 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">과제 완료 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가공도 차단 해소 후 3종 PDF 확정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">도면별 출력 경로</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">현재 판정에서 특히 주의할 점</x:t>
   </x:si>
   <x:si>
@@ -150,9 +282,6 @@
     <x:t xml:space="preserve">근거·비고</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">가공도</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">출력 흐름</x:t>
   </x:si>
   <x:si>
@@ -168,9 +297,6 @@
     <x:t xml:space="preserve">△</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">출력 불가</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Excel 가공도 템플릿 + 2D 캡처</x:t>
   </x:si>
   <x:si>
@@ -207,9 +333,6 @@
     <x:t xml:space="preserve">생산 기준상 대각 선형 치수를 적용하지 않기로 결정하고 기존 위치 치수를 유지</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">공통</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">성능</x:t>
   </x:si>
   <x:si>
@@ -297,9 +420,6 @@
     <x:t xml:space="preserve">제작·조립·설치·가공</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">표제부</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">도면 종류 자동 표기</x:t>
   </x:si>
   <x:si>
@@ -369,9 +489,6 @@
     <x:t xml:space="preserve">UDA가 아니라 앱이 생성한 BOM 순번 사용</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">BOM</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">BOM 테이블 출력</x:t>
   </x:si>
   <x:si>
@@ -525,9 +642,6 @@
     <x:t xml:space="preserve">접합 위치·연결 치수 코드 완료, 최종 PDF 검증 대기</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">설치도</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">도면 연결부재·외부 Assembly 표시</x:t>
   </x:si>
   <x:si>
@@ -594,24 +708,9 @@
     <x:t xml:space="preserve">가로화·축척·실선/은선 실기 재확인 필요</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">미리보기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3D 미리보기 형상 풍선 숨김</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">공통 장면 생성 후 3D Review Note 정리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3D 미리보기 풍선은 숨기고 PDF의 Hole·SlotHole·EarthBoss 풍선은 유지; 실기 확인 대기</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">긴 Note 처리 정책</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">분석 필요</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">고정 크기 Note 박스</x:t>
   </x:si>
   <x:si>
@@ -687,9 +786,6 @@
     <x:t xml:space="preserve">STRU 단위 4종 도면 일괄 출력</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">부분 구현</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">제작·조립·설치는 경로 존재, 가공도 제외</x:t>
   </x:si>
   <x:si>
@@ -801,9 +897,6 @@
     <x:t xml:space="preserve">가공도 자동 일괄 출력</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">개발 필요</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">자동 STRU 루프에서 현재 강제 제외</x:t>
   </x:si>
   <x:si>
@@ -876,9 +969,6 @@
     <x:t xml:space="preserve">PAINT CODE (STRU UDA PNT)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">개발 대기</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Input 165 값칸은 있으나 현재 공백 유지</x:t>
   </x:si>
   <x:si>
@@ -921,9 +1011,6 @@
     <x:t xml:space="preserve">2D Drawing 선·홀·모서리 미표시</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">API 대기</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">GenerateEdgeData + Hidden Line 캡처</x:t>
   </x:si>
   <x:si>
@@ -975,6 +1062,15 @@
     <x:t xml:space="preserve">템플릿 API</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">빈 셀 테두리 삭제 시 고정 템플릿 테두리 보존</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">빈 Note 영역의 테두리만 제거하고 고정 템플릿 테두리는 보존</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API 수정본 적용 후 빈 Note 영역 테두리 제거와 고정 템플릿 테두리 보존 확인 완료</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">템플릿 Input 다량 적용 시 보호된 메모리 충돌</x:t>
   </x:si>
   <x:si>
@@ -1200,6 +1296,9 @@
     <x:t xml:space="preserve">입력 UI·저장·길이 정책</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">빈 Note 영역 테두리 선택 제거 API 해결 완료. 입력 UI·긴 텍스트 정책은 별도 개발 필요</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Rev</x:t>
   </x:si>
   <x:si>
@@ -1306,12 +1405,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ISO 미리보기 상태 정리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">진입 시 Measure·ShapeDrawing 초기화</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ISO에는 BOM 풍선만 유지됨을 사내 실기 확인</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2D 출력 후 임시 치수 정리</x:t>
@@ -1667,7 +1760,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -1719,23 +1812,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
@@ -1779,17 +1866,23 @@
     <x:xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <x:alignment vertical="center"/>
@@ -1826,9 +1919,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2356,28 +2446,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34.04999923706055" customHeight="1">
-      <x:c r="A1" s="23" t="s">
+      <x:c r="A1" s="21" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="23"/>
-      <x:c r="C1" s="23"/>
-      <x:c r="D1" s="23"/>
-      <x:c r="E1" s="23"/>
-      <x:c r="F1" s="23"/>
-      <x:c r="G1" s="23"/>
-      <x:c r="H1" s="23"/>
+      <x:c r="B1" s="21"/>
+      <x:c r="C1" s="21"/>
+      <x:c r="D1" s="21"/>
+      <x:c r="E1" s="21"/>
+      <x:c r="F1" s="21"/>
+      <x:c r="G1" s="21"/>
+      <x:c r="H1" s="21"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="24" t="s">
+      <x:c r="A2" s="22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="24"/>
-      <x:c r="C2" s="24"/>
-      <x:c r="D2" s="24"/>
-      <x:c r="E2" s="24"/>
-      <x:c r="F2" s="24"/>
-      <x:c r="G2" s="24"/>
-      <x:c r="H2" s="24"/>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3"/>
@@ -2388,54 +2478,54 @@
       <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="25" t="s">
+      <x:c r="A4" s="23" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="26"/>
-      <x:c r="C4" s="31" t="s">
+      <x:c r="B4" s="24"/>
+      <x:c r="C4" s="29" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D4" s="32"/>
-      <x:c r="E4" s="33" t="s">
+      <x:c r="D4" s="30"/>
+      <x:c r="E4" s="31" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F4" s="34"/>
-      <x:c r="G4" s="35" t="s">
+      <x:c r="F4" s="32"/>
+      <x:c r="G4" s="33" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H4" s="36"/>
+      <x:c r="H4" s="34"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="27" t="n">
+      <x:c r="A5" s="25" t="n">
         <x:f>COUNTA('개발 항목'!$D$6:$D$79)</x:f>
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B5" s="28"/>
-      <x:c r="C5" s="27" t="n">
+      <x:c r="B5" s="26"/>
+      <x:c r="C5" s="25" t="n">
         <x:f>COUNTIF('개발 항목'!$I$6:$I$79,"완료")</x:f>
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D5" s="28"/>
-      <x:c r="E5" s="27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="26"/>
+      <x:c r="E5" s="25" t="n">
         <x:f>COUNTIF('개발 항목'!$I$6:$I$79,"실기 검증 대기")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="28"/>
-      <x:c r="G5" s="27" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F5" s="26"/>
+      <x:c r="G5" s="25" t="n">
         <x:f>COUNTIFS('개발 항목'!$E$6:$E$79,"○",'개발 항목'!$H$6:$H$79,"&lt;&gt;O")</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H5" s="28"/>
+      <x:c r="H5" s="26"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="29"/>
-      <x:c r="B6" s="30"/>
-      <x:c r="C6" s="29"/>
-      <x:c r="D6" s="30"/>
-      <x:c r="E6" s="29"/>
-      <x:c r="F6" s="30"/>
-      <x:c r="G6" s="29"/>
-      <x:c r="H6" s="30"/>
+      <x:c r="A6" s="27"/>
+      <x:c r="B6" s="28"/>
+      <x:c r="C6" s="27"/>
+      <x:c r="D6" s="28"/>
+      <x:c r="E6" s="27"/>
+      <x:c r="F6" s="28"/>
+      <x:c r="G6" s="27"/>
+      <x:c r="H6" s="28"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -2446,16 +2536,16 @@
       <x:c r="F7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="40" t="s">
+      <x:c r="A8" s="20" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="40"/>
-      <x:c r="C8" s="40"/>
-      <x:c r="D8" s="40"/>
-      <x:c r="E8" s="40"/>
-      <x:c r="F8" s="40"/>
-      <x:c r="G8" s="40"/>
-      <x:c r="H8" s="40"/>
+      <x:c r="B8" s="20"/>
+      <x:c r="C8" s="20"/>
+      <x:c r="D8" s="20"/>
+      <x:c r="E8" s="20"/>
+      <x:c r="F8" s="20"/>
+      <x:c r="G8" s="20"/>
+      <x:c r="H8" s="20"/>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="6" t="s">
@@ -2484,210 +2574,210 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="8" t="n">
+      <x:c r="A10" s="8">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="str">
-        <x:v>가공도</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="str">
-        <x:v>첫 2D 캡처 AccessViolation</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>출력 불가</x:v>
-      </x:c>
-      <x:c r="E10" s="7" t="str">
-        <x:v>가공도·4종 일괄 차단</x:v>
-      </x:c>
-      <x:c r="F10" s="7" t="str">
-        <x:v>API 요청 전달 후 수정본 재검증</x:v>
-      </x:c>
-      <x:c r="G10" s="7" t="str">
-        <x:v>가공도 캡처 경로</x:v>
-      </x:c>
-      <x:c r="H10" s="54" t="n">
+      <x:c r="B10" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H10" s="9">
         <x:v>46225</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="8" t="n">
+      <x:c r="A11" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="str">
-        <x:v>설치도</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="str">
-        <x:v>기준 Part 끝단→연결 Part 접합측 모서리 치수</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>실기 검증 대기</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="str">
-        <x:v>설치 위치 정보 신뢰성</x:v>
-      </x:c>
-      <x:c r="F11" s="7" t="str">
-        <x:v>대표 STRU PDF로 실제 끝단·모서리 검증</x:v>
-      </x:c>
-      <x:c r="G11" s="7" t="str">
-        <x:v>설치도 PreparedDimensions</x:v>
-      </x:c>
-      <x:c r="H11" s="54" t="n">
+      <x:c r="B11" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G11" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H11" s="9">
         <x:v>46225</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="8" t="n">
+      <x:c r="A12" s="8">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="str">
-        <x:v>공통</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="str">
-        <x:v>2D 모서리·홀·실선/은선 누락</x:v>
-      </x:c>
-      <x:c r="D12" s="8" t="str">
-        <x:v>API 대기</x:v>
-      </x:c>
-      <x:c r="E12" s="7" t="str">
-        <x:v>형상 누락</x:v>
-      </x:c>
-      <x:c r="F12" s="7" t="str">
-        <x:v>2026-07-23 API 배포분으로 재검증</x:v>
-      </x:c>
-      <x:c r="G12" s="7" t="str">
-        <x:v>형상·은선 렌더</x:v>
-      </x:c>
-      <x:c r="H12" s="54" t="n">
+      <x:c r="B12" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H12" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="8" t="n">
+      <x:c r="A13" s="8">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="str">
-        <x:v>가공도</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>EA 축척·풍선·은선</x:v>
-      </x:c>
-      <x:c r="D13" s="8" t="str">
-        <x:v>API 대기</x:v>
-      </x:c>
-      <x:c r="E13" s="7" t="str">
-        <x:v>가공 치수·표현</x:v>
-      </x:c>
-      <x:c r="F13" s="7" t="str">
-        <x:v>신 DLL 적용 후 EA 실기</x:v>
-      </x:c>
-      <x:c r="G13" s="7" t="str">
-        <x:v>EA 렌더·SDK</x:v>
-      </x:c>
-      <x:c r="H13" s="54" t="n">
+      <x:c r="B13" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H13" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14" s="8" t="n">
+      <x:c r="A14" s="8">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B14" s="7" t="str">
-        <x:v>BOM</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>Q'TY·MA·FA 실제 데이터</x:v>
-      </x:c>
-      <x:c r="D14" s="8" t="str">
-        <x:v>개발 필요</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="str">
-        <x:v>BOM 생산정보 오류</x:v>
-      </x:c>
-      <x:c r="F14" s="7" t="str">
-        <x:v>UDA/집계 규칙 확정</x:v>
-      </x:c>
-      <x:c r="G14" s="7" t="str">
-        <x:v>현재 임시값</x:v>
-      </x:c>
-      <x:c r="H14" s="54" t="n">
+      <x:c r="B14" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H14" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15" s="8" t="n">
+      <x:c r="A15" s="8">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B15" s="7" t="str">
-        <x:v>표제부</x:v>
-      </x:c>
-      <x:c r="C15" s="7" t="str">
-        <x:v>Paint Code(PNT)·DP No·Note·Rev</x:v>
-      </x:c>
-      <x:c r="D15" s="8" t="str">
-        <x:v>개발 대기</x:v>
-      </x:c>
-      <x:c r="E15" s="7" t="str">
-        <x:v>생산/문서정보 누락</x:v>
-      </x:c>
-      <x:c r="F15" s="7" t="str">
-        <x:v>PNT→Input 165 구현과 입력 데이터 확정</x:v>
-      </x:c>
-      <x:c r="G15" s="7" t="str">
-        <x:v>PNT UDA·템플릿 자리</x:v>
-      </x:c>
-      <x:c r="H15" s="54" t="n">
+      <x:c r="B15" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
-      <x:c r="A16" s="8" t="n">
+      <x:c r="A16" s="8">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B16" s="7" t="str">
-        <x:v>공통</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="str">
-        <x:v>기울어진 부재·라운드·모떼기</x:v>
-      </x:c>
-      <x:c r="D16" s="8" t="str">
-        <x:v>분석 필요</x:v>
-      </x:c>
-      <x:c r="E16" s="7" t="str">
-        <x:v>치수·형상 표현</x:v>
-      </x:c>
-      <x:c r="F16" s="7" t="str">
-        <x:v>적용 범위와 필터 조건 확정</x:v>
-      </x:c>
-      <x:c r="G16" s="7" t="str">
-        <x:v>형상·치수 분석</x:v>
-      </x:c>
-      <x:c r="H16" s="54" t="n">
+      <x:c r="B16" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H16" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
-      <x:c r="A17" s="8" t="n">
+      <x:c r="A17" s="8">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B17" s="7" t="str">
-        <x:v>최종</x:v>
-      </x:c>
-      <x:c r="C17" s="7" t="str">
-        <x:v>제작·가공·설치도 최종 생산 출력</x:v>
-      </x:c>
-      <x:c r="D17" s="8" t="str">
-        <x:v>부분 구현</x:v>
-      </x:c>
-      <x:c r="E17" s="7" t="str">
-        <x:v>과제 완료 기준</x:v>
-      </x:c>
-      <x:c r="F17" s="7" t="str">
-        <x:v>가공도 차단 해소 후 3종 PDF 확정</x:v>
-      </x:c>
-      <x:c r="G17" s="7" t="str">
-        <x:v>도면별 출력 경로</x:v>
-      </x:c>
-      <x:c r="H17" s="54" t="n">
+      <x:c r="B17" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H17" s="9">
         <x:v>46226</x:v>
       </x:c>
     </x:row>
@@ -2699,7 +2789,7 @@
       <x:c r="E18" s="7"/>
       <x:c r="F18" s="7"/>
       <x:c r="G18" s="7"/>
-      <x:c r="H18" s="54"/>
+      <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19"/>
@@ -2710,96 +2800,89 @@
       <x:c r="F19"/>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
-      <x:c r="A20" s="40" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B20" s="40"/>
-      <x:c r="C20" s="40"/>
-      <x:c r="D20" s="40"/>
-      <x:c r="E20" s="40"/>
-      <x:c r="F20" s="40"/>
-      <x:c r="G20" s="40"/>
-      <x:c r="H20" s="40"/>
+      <x:c r="A20" s="20" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B20" s="20"/>
+      <x:c r="C20" s="20"/>
+      <x:c r="D20" s="20"/>
+      <x:c r="E20" s="20"/>
+      <x:c r="F20" s="20"/>
+      <x:c r="G20" s="20"/>
+      <x:c r="H20" s="20"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B21" s="37" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C21" s="38"/>
-      <x:c r="D21" s="38"/>
-      <x:c r="E21" s="38"/>
-      <x:c r="F21" s="38"/>
-      <x:c r="G21" s="38"/>
-      <x:c r="H21" s="39"/>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C21" s="18"/>
+      <x:c r="D21" s="18"/>
+      <x:c r="E21" s="18"/>
+      <x:c r="F21" s="18"/>
+      <x:c r="G21" s="18"/>
+      <x:c r="H21" s="19"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B22" s="37" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C22" s="38"/>
-      <x:c r="D22" s="38"/>
-      <x:c r="E22" s="38"/>
-      <x:c r="F22" s="38"/>
-      <x:c r="G22" s="38"/>
-      <x:c r="H22" s="39"/>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C22" s="18"/>
+      <x:c r="D22" s="18"/>
+      <x:c r="E22" s="18"/>
+      <x:c r="F22" s="18"/>
+      <x:c r="G22" s="18"/>
+      <x:c r="H22" s="19"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B23" s="37" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C23" s="38"/>
-      <x:c r="D23" s="38"/>
-      <x:c r="E23" s="38"/>
-      <x:c r="F23" s="38"/>
-      <x:c r="G23" s="38"/>
-      <x:c r="H23" s="39"/>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C23" s="18"/>
+      <x:c r="D23" s="18"/>
+      <x:c r="E23" s="18"/>
+      <x:c r="F23" s="18"/>
+      <x:c r="G23" s="18"/>
+      <x:c r="H23" s="19"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B24" s="37" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C24" s="38"/>
-      <x:c r="D24" s="38"/>
-      <x:c r="E24" s="38"/>
-      <x:c r="F24" s="38"/>
-      <x:c r="G24" s="38"/>
-      <x:c r="H24" s="39"/>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C24" s="18"/>
+      <x:c r="D24" s="18"/>
+      <x:c r="E24" s="18"/>
+      <x:c r="F24" s="18"/>
+      <x:c r="G24" s="18"/>
+      <x:c r="H24" s="19"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B25" s="37" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C25" s="38"/>
-      <x:c r="D25" s="38"/>
-      <x:c r="E25" s="38"/>
-      <x:c r="F25" s="38"/>
-      <x:c r="G25" s="38"/>
-      <x:c r="H25" s="39"/>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C25" s="18"/>
+      <x:c r="D25" s="18"/>
+      <x:c r="E25" s="18"/>
+      <x:c r="F25" s="18"/>
+      <x:c r="G25" s="18"/>
+      <x:c r="H25" s="19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B24:H24"/>
-    <x:mergeCell ref="B25:H25"/>
-    <x:mergeCell ref="A8:H8"/>
-    <x:mergeCell ref="A20:H20"/>
-    <x:mergeCell ref="B22:H22"/>
-    <x:mergeCell ref="B23:H23"/>
-    <x:mergeCell ref="B21:H21"/>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:B4"/>
@@ -2810,6 +2893,13 @@
     <x:mergeCell ref="E5:F6"/>
     <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="G5:H6"/>
+    <x:mergeCell ref="B24:H24"/>
+    <x:mergeCell ref="B25:H25"/>
+    <x:mergeCell ref="A8:H8"/>
+    <x:mergeCell ref="A20:H20"/>
+    <x:mergeCell ref="B22:H22"/>
+    <x:mergeCell ref="B23:H23"/>
+    <x:mergeCell ref="B21:H21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2838,122 +2928,122 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34.04999923706055" customHeight="1">
-      <x:c r="A1" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B1" s="17"/>
-      <x:c r="C1" s="17"/>
-      <x:c r="D1" s="17"/>
-      <x:c r="E1" s="17"/>
-      <x:c r="F1" s="17"/>
-      <x:c r="G1" s="17"/>
-      <x:c r="H1" s="17"/>
-      <x:c r="I1" s="18"/>
-      <x:c r="J1" s="17"/>
-      <x:c r="K1" s="17"/>
-      <x:c r="L1" s="17"/>
-      <x:c r="M1" s="17"/>
-      <x:c r="N1" s="17"/>
-      <x:c r="O1" s="17"/>
-      <x:c r="P1" s="17"/>
-      <x:c r="Q1" s="17"/>
-      <x:c r="R1" s="17"/>
+      <x:c r="A1" s="35" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B1" s="35"/>
+      <x:c r="C1" s="35"/>
+      <x:c r="D1" s="35"/>
+      <x:c r="E1" s="35"/>
+      <x:c r="F1" s="35"/>
+      <x:c r="G1" s="35"/>
+      <x:c r="H1" s="35"/>
+      <x:c r="I1" s="36"/>
+      <x:c r="J1" s="35"/>
+      <x:c r="K1" s="35"/>
+      <x:c r="L1" s="35"/>
+      <x:c r="M1" s="35"/>
+      <x:c r="N1" s="35"/>
+      <x:c r="O1" s="35"/>
+      <x:c r="P1" s="35"/>
+      <x:c r="Q1" s="35"/>
+      <x:c r="R1" s="35"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="19" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B2" s="19"/>
-      <x:c r="C2" s="19"/>
-      <x:c r="D2" s="19"/>
-      <x:c r="E2" s="19"/>
-      <x:c r="F2" s="19"/>
-      <x:c r="G2" s="19"/>
-      <x:c r="H2" s="19"/>
-      <x:c r="I2" s="20"/>
-      <x:c r="J2" s="19"/>
-      <x:c r="K2" s="19"/>
-      <x:c r="L2" s="19"/>
-      <x:c r="M2" s="19"/>
-      <x:c r="N2" s="19"/>
-      <x:c r="O2" s="19"/>
-      <x:c r="P2" s="19"/>
-      <x:c r="Q2" s="19"/>
-      <x:c r="R2" s="19"/>
+      <x:c r="A2" s="37" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B2" s="37"/>
+      <x:c r="C2" s="37"/>
+      <x:c r="D2" s="37"/>
+      <x:c r="E2" s="37"/>
+      <x:c r="F2" s="37"/>
+      <x:c r="G2" s="37"/>
+      <x:c r="H2" s="37"/>
+      <x:c r="I2" s="38"/>
+      <x:c r="J2" s="37"/>
+      <x:c r="K2" s="37"/>
+      <x:c r="L2" s="37"/>
+      <x:c r="M2" s="37"/>
+      <x:c r="N2" s="37"/>
+      <x:c r="O2" s="37"/>
+      <x:c r="P2" s="37"/>
+      <x:c r="Q2" s="37"/>
+      <x:c r="R2" s="37"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="21" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B3" s="21"/>
-      <x:c r="C3" s="21"/>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="21"/>
-      <x:c r="F3" s="21"/>
-      <x:c r="G3" s="21"/>
-      <x:c r="H3" s="21"/>
-      <x:c r="I3" s="22"/>
-      <x:c r="J3" s="21"/>
-      <x:c r="K3" s="21"/>
-      <x:c r="L3" s="21"/>
-      <x:c r="M3" s="21"/>
-      <x:c r="N3" s="21"/>
-      <x:c r="O3" s="21"/>
-      <x:c r="P3" s="21"/>
-      <x:c r="Q3" s="21"/>
-      <x:c r="R3" s="21"/>
+      <x:c r="A3" s="39" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
+      <x:c r="H3" s="39"/>
+      <x:c r="I3" s="40"/>
+      <x:c r="J3" s="39"/>
+      <x:c r="K3" s="39"/>
+      <x:c r="L3" s="39"/>
+      <x:c r="M3" s="39"/>
+      <x:c r="N3" s="39"/>
+      <x:c r="O3" s="39"/>
+      <x:c r="P3" s="39"/>
+      <x:c r="Q3" s="39"/>
+      <x:c r="R3" s="39"/>
     </x:row>
     <x:row r="5" ht="43.95000076293945" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E5" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G5" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H5" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I5" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J5" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K5" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="L5" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="M5" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="N5" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="O5" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="P5" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="Q5" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="R5"/>
     </x:row>
@@ -2962,40 +3052,40 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E6" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F6" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G6" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H6" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>53</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K6" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L6" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M6" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N6" s="9">
         <x:v>46168</x:v>
@@ -3005,7 +3095,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="s">
-        <x:v>56</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="R6"/>
     </x:row>
@@ -3014,40 +3104,40 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E7" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F7" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G7" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H7" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K7" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L7" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M7" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N7" s="9"/>
       <x:c r="O7" s="9">
@@ -3057,7 +3147,7 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="Q7" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="R7"/>
     </x:row>
@@ -3066,40 +3156,40 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>66</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>67</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E8" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H8" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K8" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L8" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N8" s="9">
         <x:v>46224</x:v>
@@ -3111,7 +3201,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="R8"/>
     </x:row>
@@ -3120,40 +3210,40 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
-        <x:v>66</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E9" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F9" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G9" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H9" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K9" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L9" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M9" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N9" s="9">
         <x:v>46225</x:v>
@@ -3165,7 +3255,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="R9"/>
     </x:row>
@@ -3174,40 +3264,40 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="8" t="s">
-        <x:v>73</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E10" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G10" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H10" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K10" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L10" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M10" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N10" s="9">
         <x:v>46225</x:v>
@@ -3219,7 +3309,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="R10"/>
     </x:row>
@@ -3228,40 +3318,40 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E11" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F11" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G11" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H11" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K11" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L11" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M11" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N11" s="9">
         <x:v>46156</x:v>
@@ -3273,7 +3363,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="R11"/>
     </x:row>
@@ -3282,40 +3372,40 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C12" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
-        <x:v>84</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E12" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F12" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G12" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H12" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I12" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
-        <x:v>85</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K12" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L12" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M12" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N12" s="9">
         <x:v>46224</x:v>
@@ -3327,7 +3417,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="s">
-        <x:v>86</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="R12"/>
     </x:row>
@@ -3336,40 +3426,40 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="8" t="s">
-        <x:v>87</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C13" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
-        <x:v>88</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E13" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F13" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G13" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H13" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I13" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J13" s="7" t="s">
-        <x:v>89</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K13" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L13" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M13" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N13" s="9">
         <x:v>46224</x:v>
@@ -3381,7 +3471,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q13" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="R13"/>
     </x:row>
@@ -3390,40 +3480,40 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D14" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E14" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F14" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G14" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H14" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I14" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J14" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K14" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L14" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M14" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N14" s="9">
         <x:v>46156</x:v>
@@ -3433,7 +3523,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="R14"/>
     </x:row>
@@ -3442,40 +3532,40 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D15" s="7" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E15" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F15" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G15" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H15" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I15" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J15" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K15" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L15" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M15" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N15" s="9">
         <x:v>46155</x:v>
@@ -3485,7 +3575,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="s">
-        <x:v>98</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="R15"/>
     </x:row>
@@ -3494,40 +3584,40 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D16" s="7" t="s">
-        <x:v>100</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E16" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F16" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G16" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H16" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I16" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J16" s="7" t="s">
-        <x:v>101</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K16" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L16" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M16" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N16" s="9">
         <x:v>46224</x:v>
@@ -3539,7 +3629,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="R16"/>
     </x:row>
@@ -3548,40 +3638,40 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
-        <x:v>103</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G17" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H17" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J17" s="7" t="s">
-        <x:v>104</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K17" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L17" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M17" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N17" s="9">
         <x:v>46223</x:v>
@@ -3593,7 +3683,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q17" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="R17"/>
     </x:row>
@@ -3602,40 +3692,40 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
-        <x:v>106</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E18" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G18" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H18" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I18" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J18" s="7" t="s">
-        <x:v>107</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K18" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L18" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M18" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N18" s="9">
         <x:v>46188</x:v>
@@ -3645,7 +3735,7 @@
         <x:v>46223</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="R18"/>
     </x:row>
@@ -3654,40 +3744,40 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
-        <x:v>109</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E19" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G19" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H19" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I19" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J19" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K19" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L19" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M19" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N19" s="9">
         <x:v>46156</x:v>
@@ -3697,7 +3787,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q19" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="R19"/>
     </x:row>
@@ -3706,40 +3796,40 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
-        <x:v>112</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F20" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G20" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H20" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I20" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J20" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K20" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L20" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M20" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N20" s="9">
         <x:v>46156</x:v>
@@ -3749,7 +3839,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="R20"/>
     </x:row>
@@ -3758,40 +3848,40 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C21" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F21" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G21" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H21" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I21" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J21" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K21" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L21" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M21" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N21" s="9">
         <x:v>46156</x:v>
@@ -3801,7 +3891,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q21" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="R21"/>
     </x:row>
@@ -3810,40 +3900,40 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E22" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F22" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G22" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H22" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I22" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J22" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K22" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L22" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M22" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N22" s="9">
         <x:v>46156</x:v>
@@ -3853,7 +3943,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="s">
-        <x:v>118</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="R22"/>
     </x:row>
@@ -3862,40 +3952,40 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
-        <x:v>120</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E23" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F23" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G23" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H23" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I23" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J23" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K23" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L23" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M23" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N23" s="9">
         <x:v>46125</x:v>
@@ -3905,7 +3995,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q23" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R23"/>
     </x:row>
@@ -3914,40 +4004,40 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E24" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F24" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G24" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H24" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I24" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J24" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K24" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L24" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M24" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N24" s="9">
         <x:v>46125</x:v>
@@ -3957,7 +4047,7 @@
         <x:v>46156</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="R24"/>
     </x:row>
@@ -3966,40 +4056,40 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
-        <x:v>126</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E25" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F25" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H25" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I25" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J25" s="7" t="s">
-        <x:v>127</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K25" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L25" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M25" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N25" s="9">
         <x:v>46125</x:v>
@@ -4011,7 +4101,7 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="Q25" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="R25"/>
     </x:row>
@@ -4020,40 +4110,40 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F26" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G26" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I26" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J26" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="K26" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L26" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M26" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N26" s="9">
         <x:v>46125</x:v>
@@ -4063,7 +4153,7 @@
         <x:v>46155</x:v>
       </x:c>
       <x:c r="Q26" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="R26"/>
     </x:row>
@@ -4072,40 +4162,40 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C27" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F27" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G27" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H27" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I27" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J27" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K27" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L27" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M27" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N27" s="9">
         <x:v>46125</x:v>
@@ -4115,7 +4205,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q27" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="R27"/>
     </x:row>
@@ -4124,40 +4214,40 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="8" t="s">
-        <x:v>87</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C28" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D28" s="7" t="s">
-        <x:v>135</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E28" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F28" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G28" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I28" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J28" s="7" t="s">
-        <x:v>136</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K28" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L28" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M28" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N28" s="9">
         <x:v>46225</x:v>
@@ -4169,7 +4259,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q28" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="R28"/>
     </x:row>
@@ -4178,40 +4268,40 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B29" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C29" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E29" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F29" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G29" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I29" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J29" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K29" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L29" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M29" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N29" s="9">
         <x:v>46134</x:v>
@@ -4223,7 +4313,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q29" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="R29"/>
     </x:row>
@@ -4232,40 +4322,40 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="8" t="s">
-        <x:v>141</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="7" t="s">
-        <x:v>142</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E30" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F30" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G30" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H30" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I30" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J30" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="K30" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L30" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M30" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N30" s="9">
         <x:v>46206</x:v>
@@ -4277,7 +4367,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q30" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="R30"/>
     </x:row>
@@ -4286,40 +4376,40 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B31" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>145</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D31" s="7" t="s">
-        <x:v>146</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E31" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F31" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G31" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H31" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I31" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J31" s="7" t="s">
-        <x:v>147</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K31" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L31" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M31" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N31" s="9">
         <x:v>46215</x:v>
@@ -4331,7 +4421,7 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="Q31" s="7" t="s">
-        <x:v>148</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="R31"/>
     </x:row>
@@ -4340,40 +4430,40 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B32" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C32" s="8" t="s">
-        <x:v>149</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D32" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E32" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F32" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G32" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H32" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I32" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J32" s="7" t="s">
-        <x:v>151</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K32" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L32" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M32" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N32" s="9">
         <x:v>46225</x:v>
@@ -4385,7 +4475,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q32" s="7" t="s">
-        <x:v>152</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="R32"/>
     </x:row>
@@ -4394,40 +4484,40 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B33" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C33" s="8" t="s">
-        <x:v>153</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D33" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E33" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F33" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G33" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H33" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I33" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J33" s="7" t="s">
-        <x:v>155</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K33" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L33" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M33" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N33" s="9">
         <x:v>46225</x:v>
@@ -4439,7 +4529,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q33" s="7" t="s">
-        <x:v>156</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="R33"/>
     </x:row>
@@ -4448,40 +4538,40 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="10" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
-        <x:v>157</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D34" s="10" t="s">
-        <x:v>158</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E34" s="10" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F34" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G34" s="10" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H34" s="10" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I34" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J34" s="10" t="s">
-        <x:v>159</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K34" s="10" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L34" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M34" s="10" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N34" s="13">
         <x:v>46225</x:v>
@@ -4493,7 +4583,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q34" s="10" t="s">
-        <x:v>160</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="R34"/>
     </x:row>
@@ -4502,40 +4592,40 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B35" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C35" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D35" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E35" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F35" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G35" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H35" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I35" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J35" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K35" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L35" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M35" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N35" s="9">
         <x:v>46155</x:v>
@@ -4545,7 +4635,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q35" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="R35"/>
     </x:row>
@@ -4554,40 +4644,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B36" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C36" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D36" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E36" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F36" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G36" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H36" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I36" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J36" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K36" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L36" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M36" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N36" s="9">
         <x:v>46155</x:v>
@@ -4597,7 +4687,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q36" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="R36"/>
     </x:row>
@@ -4606,40 +4696,40 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B37" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C37" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D37" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E37" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F37" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G37" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H37" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I37" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J37" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K37" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L37" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M37" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N37" s="9">
         <x:v>46155</x:v>
@@ -4649,7 +4739,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q37" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="R37"/>
     </x:row>
@@ -4658,40 +4748,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
-        <x:v>172</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E38" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F38" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G38" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H38" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I38" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J38" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K38" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L38" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M38" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N38" s="9">
         <x:v>46224</x:v>
@@ -4701,7 +4791,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q38" s="7" t="s">
-        <x:v>174</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="R38"/>
     </x:row>
@@ -4710,40 +4800,40 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="8" t="s">
-        <x:v>175</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C39" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D39" s="7" t="s">
-        <x:v>176</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E39" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F39" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G39" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H39" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I39" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J39" s="7" t="s">
-        <x:v>177</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K39" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L39" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M39" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N39" s="9">
         <x:v>46224</x:v>
@@ -4753,7 +4843,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q39" s="7" t="s">
-        <x:v>178</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="R39"/>
     </x:row>
@@ -4762,40 +4852,40 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B40" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D40" s="7" t="s">
-        <x:v>179</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E40" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F40" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G40" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H40" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I40" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J40" s="7" t="s">
-        <x:v>180</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K40" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L40" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M40" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N40" s="9">
         <x:v>46224</x:v>
@@ -4805,7 +4895,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q40" s="7" t="s">
-        <x:v>181</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="R40"/>
     </x:row>
@@ -4814,40 +4904,40 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B41" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C41" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D41" s="7" t="s">
-        <x:v>183</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E41" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F41" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G41" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H41" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I41" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J41" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K41" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L41" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M41" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N41" s="9">
         <x:v>46195</x:v>
@@ -4857,7 +4947,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q41" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="R41"/>
     </x:row>
@@ -4866,40 +4956,40 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B42" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C42" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D42" s="7" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E42" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F42" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G42" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H42" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I42" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J42" s="7" t="s">
-        <x:v>187</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K42" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L42" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M42" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N42" s="9">
         <x:v>46164</x:v>
@@ -4909,7 +4999,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q42" s="7" t="s">
-        <x:v>188</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="R42"/>
     </x:row>
@@ -4918,40 +5008,40 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B43" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>189</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D43" s="7" t="s">
-        <x:v>190</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E43" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F43" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G43" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H43" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I43" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J43" s="7" t="s">
-        <x:v>191</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K43" s="8" t="s">
-        <x:v>192</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L43" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M43" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N43" s="9">
         <x:v>46188</x:v>
@@ -4961,59 +5051,61 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q43" s="7" t="s">
-        <x:v>193</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="R43"/>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
-      <x:c r="A44" s="8">
+      <x:c r="A44" s="8" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B44" s="8" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C44" s="8" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D44" s="7" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="E44" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F44" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G44" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H44" s="8" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="I44" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J44" s="7" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="K44" s="8" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="L44" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M44" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N44" s="9">
+      <x:c r="B44" s="8" t="str">
+        <x:v>가공도</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="str">
+        <x:v>미리보기</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="str">
+        <x:v>3D 미리보기 형상 풍선 숨김</x:v>
+      </x:c>
+      <x:c r="E44" s="8" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F44" s="8" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="G44" s="8" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="H44" s="8" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="I44" s="8" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="J44" s="7" t="str">
+        <x:v>3D 미리보기의 Review Note 풍선을 정리하고 PDF 출력 풍선은 유지</x:v>
+      </x:c>
+      <x:c r="K44" s="8" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="L44" s="8" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M44" s="8" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="N44" s="53" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="O44" s="9"/>
-      <x:c r="P44" s="9">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="Q44" s="7" t="s">
-        <x:v>197</x:v>
+      <x:c r="O44" s="53" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="P44" s="53" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="Q44" s="7" t="str">
+        <x:v>사용자 실기 확인 완료: 3D 미리보기의 Hole·SlotHole·EarthBoss 풍선은 숨기고 PDF 풍선은 유지</x:v>
       </x:c>
       <x:c r="R44"/>
     </x:row>
@@ -5022,40 +5114,40 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B45" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C45" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D45" s="7" t="s">
-        <x:v>198</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E45" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F45" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G45" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H45" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I45" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F45" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G45" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H45" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I45" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="J45" s="7" t="s">
-        <x:v>200</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K45" s="8" t="s">
-        <x:v>201</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="L45" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M45" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N45" s="9"/>
       <x:c r="O45" s="9"/>
@@ -5063,7 +5155,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q45" s="7" t="s">
-        <x:v>202</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R45"/>
     </x:row>
@@ -5072,40 +5164,40 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C46" s="8" t="s">
-        <x:v>203</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D46" s="7" t="s">
-        <x:v>204</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E46" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F46" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G46" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H46" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I46" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F46" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G46" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H46" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I46" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="J46" s="7" t="s">
-        <x:v>205</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="K46" s="8" t="s">
-        <x:v>206</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L46" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M46" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N46" s="9"/>
       <x:c r="O46" s="9"/>
@@ -5113,7 +5205,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q46" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="R46"/>
     </x:row>
@@ -5122,40 +5214,40 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B47" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>203</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D47" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E47" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F47" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G47" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H47" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I47" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F47" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G47" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H47" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I47" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="J47" s="7" t="s">
-        <x:v>209</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K47" s="8" t="s">
-        <x:v>206</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L47" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M47" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N47" s="9"/>
       <x:c r="O47" s="9"/>
@@ -5163,7 +5255,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q47" s="7" t="s">
-        <x:v>210</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="R47"/>
     </x:row>
@@ -5172,40 +5264,40 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B48" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="E48" s="8" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C48" s="8" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D48" s="7" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="E48" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F48" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G48" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H48" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I48" s="8" t="s">
-        <x:v>199</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J48" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K48" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L48" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M48" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N48" s="9"/>
       <x:c r="O48" s="9"/>
@@ -5213,7 +5305,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q48" s="7" t="s">
-        <x:v>214</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="R48"/>
     </x:row>
@@ -5222,40 +5314,40 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B49" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>215</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D49" s="7" t="s">
-        <x:v>216</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E49" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F49" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G49" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H49" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I49" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G49" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H49" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I49" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="J49" s="7" t="s">
-        <x:v>217</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K49" s="8" t="s">
-        <x:v>218</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="L49" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M49" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N49" s="9">
         <x:v>46154</x:v>
@@ -5265,7 +5357,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q49" s="7" t="s">
-        <x:v>219</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="R49"/>
     </x:row>
@@ -5274,40 +5366,40 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>215</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D50" s="7" t="s">
-        <x:v>220</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E50" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F50" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G50" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H50" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I50" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G50" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H50" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I50" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="J50" s="7" t="s">
-        <x:v>221</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="K50" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L50" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M50" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N50" s="9"/>
       <x:c r="O50" s="9"/>
@@ -5315,7 +5407,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q50" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="R50"/>
     </x:row>
@@ -5324,40 +5416,40 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B51" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D51" s="7" t="s">
-        <x:v>224</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E51" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F51" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G51" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H51" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I51" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J51" s="7" t="s">
-        <x:v>226</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K51" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L51" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M51" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N51" s="9">
         <x:v>46155</x:v>
@@ -5367,7 +5459,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q51" s="7" t="s">
-        <x:v>227</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="R51"/>
     </x:row>
@@ -5376,40 +5468,40 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C52" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="E52" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F52" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G52" s="8" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C52" s="8" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D52" s="7" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E52" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F52" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G52" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H52" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I52" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J52" s="7" t="s">
-        <x:v>229</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K52" s="8" t="s">
-        <x:v>230</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="L52" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M52" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N52" s="9">
         <x:v>46155</x:v>
@@ -5419,7 +5511,7 @@
         <x:v>46155</x:v>
       </x:c>
       <x:c r="Q52" s="7" t="s">
-        <x:v>231</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="R52"/>
     </x:row>
@@ -5428,40 +5520,40 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B53" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C53" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="E53" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F53" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G53" s="8" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C53" s="8" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D53" s="7" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="E53" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F53" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G53" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H53" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I53" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J53" s="7" t="s">
-        <x:v>233</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K53" s="8" t="s">
-        <x:v>234</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="L53" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M53" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N53" s="9">
         <x:v>46156</x:v>
@@ -5471,7 +5563,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q53" s="7" t="s">
-        <x:v>235</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="R53"/>
     </x:row>
@@ -5480,40 +5572,40 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C54" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="E54" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F54" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G54" s="8" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C54" s="8" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D54" s="7" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="E54" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F54" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G54" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H54" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I54" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J54" s="7" t="s">
-        <x:v>237</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K54" s="8" t="s">
-        <x:v>234</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="L54" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M54" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N54" s="9">
         <x:v>46156</x:v>
@@ -5523,7 +5615,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q54" s="7" t="s">
-        <x:v>238</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="R54"/>
     </x:row>
@@ -5532,40 +5624,40 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B55" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C55" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D55" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E55" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F55" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G55" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H55" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I55" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J55" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="K55" s="8" t="s">
-        <x:v>241</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="L55" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M55" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N55" s="9">
         <x:v>46224</x:v>
@@ -5577,7 +5669,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q55" s="7" t="s">
-        <x:v>242</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="R55"/>
     </x:row>
@@ -5586,40 +5678,40 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B56" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D56" s="7" t="s">
-        <x:v>243</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E56" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F56" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G56" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H56" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I56" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J56" s="7" t="s">
-        <x:v>244</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="K56" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="L56" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M56" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N56" s="9">
         <x:v>46196</x:v>
@@ -5629,7 +5721,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q56" s="7" t="s">
-        <x:v>246</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="R56"/>
     </x:row>
@@ -5638,40 +5730,40 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B57" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D57" s="7" t="s">
-        <x:v>247</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E57" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F57" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G57" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H57" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I57" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J57" s="7" t="s">
-        <x:v>248</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K57" s="8" t="s">
-        <x:v>241</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="L57" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M57" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N57" s="9">
         <x:v>46195</x:v>
@@ -5681,7 +5773,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q57" s="7" t="s">
-        <x:v>249</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="R57"/>
     </x:row>
@@ -5690,40 +5782,40 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B58" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>250</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D58" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E58" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F58" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G58" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H58" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I58" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J58" s="7" t="s">
-        <x:v>252</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K58" s="8" t="s">
-        <x:v>192</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L58" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M58" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N58" s="9">
         <x:v>46155</x:v>
@@ -5733,49 +5825,49 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q58" s="7" t="s">
-        <x:v>253</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="R58"/>
     </x:row>
-    <x:row r="59" ht="42" customHeight="1">
+    <x:row r="59" ht="42" hidden="1" customHeight="1">
       <x:c r="A59" s="8">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B59" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>254</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D59" s="7" t="s">
-        <x:v>255</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E59" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F59" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G59" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H59" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I59" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J59" s="7" t="s">
-        <x:v>256</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K59" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="L59" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M59" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N59" s="9">
         <x:v>46152</x:v>
@@ -5787,7 +5879,7 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="Q59" s="7" t="s">
-        <x:v>257</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="R59"/>
     </x:row>
@@ -5796,40 +5888,40 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B60" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D60" s="7" t="s">
-        <x:v>258</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E60" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F60" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G60" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H60" s="8" t="s">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I60" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J60" s="7" t="s">
-        <x:v>259</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K60" s="8" t="s">
-        <x:v>260</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="L60" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M60" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N60" s="9">
         <x:v>46224</x:v>
@@ -5839,7 +5931,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q60" s="7" t="s">
-        <x:v>261</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="R60"/>
     </x:row>
@@ -5848,40 +5940,40 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B61" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D61" s="7" t="s">
-        <x:v>262</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E61" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F61" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G61" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H61" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I61" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J61" s="7" t="s">
-        <x:v>264</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K61" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L61" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M61" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N61" s="9"/>
       <x:c r="O61" s="9"/>
@@ -5889,7 +5981,7 @@
         <x:v>46168</x:v>
       </x:c>
       <x:c r="Q61" s="7" t="s">
-        <x:v>265</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="R61"/>
     </x:row>
@@ -5898,40 +5990,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B62" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D62" s="7" t="s">
-        <x:v>266</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E62" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F62" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G62" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H62" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I62" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J62" s="7" t="s">
-        <x:v>267</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="K62" s="8" t="s">
-        <x:v>268</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="L62" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M62" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N62" s="9"/>
       <x:c r="O62" s="9"/>
@@ -5939,7 +6031,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q62" s="7" t="s">
-        <x:v>269</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="R62"/>
     </x:row>
@@ -5948,40 +6040,40 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B63" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C63" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D63" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E63" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F63" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G63" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H63" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I63" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J63" s="7" t="s">
-        <x:v>271</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="K63" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L63" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M63" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N63" s="9"/>
       <x:c r="O63" s="9"/>
@@ -5989,7 +6081,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q63" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="R63"/>
     </x:row>
@@ -5998,40 +6090,40 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B64" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D64" s="7" t="s">
-        <x:v>273</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E64" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F64" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G64" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H64" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I64" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J64" s="7" t="s">
-        <x:v>274</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="K64" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L64" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M64" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N64" s="9"/>
       <x:c r="O64" s="9"/>
@@ -6039,7 +6131,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q64" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="R64"/>
     </x:row>
@@ -6048,40 +6140,40 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B65" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D65" s="7" t="s">
-        <x:v>275</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E65" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F65" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G65" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H65" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I65" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J65" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K65" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L65" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M65" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N65" s="9"/>
       <x:c r="O65" s="9"/>
@@ -6089,7 +6181,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q65" s="7" t="s">
-        <x:v>276</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="R65"/>
     </x:row>
@@ -6098,40 +6190,40 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B66" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D66" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E66" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F66" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G66" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H66" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I66" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J66" s="7" t="s">
-        <x:v>278</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="K66" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L66" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M66" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N66" s="9">
         <x:v>46213</x:v>
@@ -6141,7 +6233,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q66" s="7" t="s">
-        <x:v>279</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="R66"/>
     </x:row>
@@ -6150,40 +6242,40 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D67" s="7" t="s">
-        <x:v>280</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E67" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F67" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G67" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H67" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I67" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J67" s="7" t="s">
-        <x:v>281</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="K67" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L67" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M67" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N67" s="9">
         <x:v>46213</x:v>
@@ -6193,7 +6285,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q67" s="7" t="s">
-        <x:v>282</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="R67"/>
     </x:row>
@@ -6202,40 +6294,40 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B68" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C68" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D68" s="7" t="s">
-        <x:v>283</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E68" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F68" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G68" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H68" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I68" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J68" s="7" t="s">
-        <x:v>284</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="K68" s="8" t="s">
-        <x:v>285</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="L68" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M68" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N68" s="9">
         <x:v>46224</x:v>
@@ -6245,7 +6337,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q68" s="7" t="s">
-        <x:v>286</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="R68"/>
     </x:row>
@@ -6254,40 +6346,40 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B69" s="8" t="s">
-        <x:v>141</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C69" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D69" s="7" t="s">
-        <x:v>287</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E69" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F69" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G69" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H69" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I69" s="8" t="s">
-        <x:v>288</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J69" s="7" t="s">
-        <x:v>289</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="K69" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L69" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M69" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N69" s="9">
         <x:v>46213</x:v>
@@ -6297,7 +6389,7 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="Q69" s="7" t="s">
-        <x:v>290</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="R69"/>
     </x:row>
@@ -6306,40 +6398,40 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B70" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>291</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D70" s="7" t="s">
-        <x:v>292</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E70" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F70" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G70" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H70" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I70" s="8" t="s">
-        <x:v>288</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J70" s="7" t="s">
-        <x:v>293</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="K70" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L70" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M70" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N70" s="9"/>
       <x:c r="O70" s="9"/>
@@ -6347,7 +6439,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q70" s="7" t="s">
-        <x:v>294</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="R70"/>
     </x:row>
@@ -6356,40 +6448,40 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B71" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D71" s="7" t="s">
-        <x:v>295</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="E71" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F71" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G71" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H71" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I71" s="8" t="s">
-        <x:v>288</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J71" s="7" t="s">
-        <x:v>296</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="K71" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="L71" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M71" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N71" s="9">
         <x:v>46135</x:v>
@@ -6399,7 +6491,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q71" s="7" t="s">
-        <x:v>297</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="R71"/>
     </x:row>
@@ -6408,40 +6500,40 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B72" s="8" t="s">
-        <x:v>141</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>215</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D72" s="7" t="s">
-        <x:v>298</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E72" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F72" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G72" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H72" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I72" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J72" s="7" t="s">
-        <x:v>299</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="K72" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="L72" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M72" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N72" s="9"/>
       <x:c r="O72" s="9"/>
@@ -6449,7 +6541,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q72" s="7" t="s">
-        <x:v>301</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="R72"/>
     </x:row>
@@ -6458,40 +6550,40 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B73" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D73" s="7" t="s">
-        <x:v>302</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E73" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F73" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G73" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H73" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I73" s="8" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J73" s="7" t="s">
-        <x:v>304</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="K73" s="8" t="s">
-        <x:v>305</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="L73" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M73" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N73" s="9">
         <x:v>46160</x:v>
@@ -6501,7 +6593,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q73" s="7" t="s">
-        <x:v>306</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
@@ -6509,40 +6601,40 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B74" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C74" s="8" t="s">
-        <x:v>307</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D74" s="7" t="s">
-        <x:v>308</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="E74" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F74" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G74" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H74" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I74" s="8" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J74" s="7" t="s">
-        <x:v>309</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="K74" s="8" t="s">
-        <x:v>310</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="L74" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M74" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N74" s="9">
         <x:v>46224</x:v>
@@ -6552,7 +6644,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q74" s="7" t="s">
-        <x:v>311</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
@@ -6560,40 +6652,40 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B75" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C75" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D75" s="7" t="s">
-        <x:v>312</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E75" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F75" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G75" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H75" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I75" s="8" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J75" s="7" t="s">
-        <x:v>313</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="K75" s="8" t="s">
-        <x:v>314</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="L75" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M75" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N75" s="9">
         <x:v>46206</x:v>
@@ -6603,7 +6695,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="Q75" s="7" t="s">
-        <x:v>315</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
@@ -6611,40 +6703,40 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B76" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C76" s="8" t="s">
-        <x:v>316</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D76" s="7" t="s">
-        <x:v>317</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="E76" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F76" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G76" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H76" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I76" s="8" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J76" s="7" t="s">
-        <x:v>318</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="K76" s="8" t="s">
-        <x:v>310</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="L76" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M76" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N76" s="9">
         <x:v>46154</x:v>
@@ -6654,60 +6746,60 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q76" s="7" t="s">
-        <x:v>319</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="42" customHeight="1">
-      <x:c r="A77" s="11" t="n">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="42" hidden="1" customHeight="1">
+      <x:c r="A77" s="11">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B77" s="11" t="str">
-        <x:v>공통</x:v>
-      </x:c>
-      <x:c r="C77" s="11" t="str">
-        <x:v>템플릿 API</x:v>
-      </x:c>
-      <x:c r="D77" s="12" t="str">
-        <x:v>빈 셀 테두리 삭제 시 고정 템플릿 테두리 보존</x:v>
-      </x:c>
-      <x:c r="E77" s="11" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F77" s="11" t="str">
-        <x:v>○</x:v>
-      </x:c>
-      <x:c r="G77" s="11" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="H77" s="11" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="I77" s="11" t="str">
-        <x:v>완료</x:v>
-      </x:c>
-      <x:c r="J77" s="12" t="str">
-        <x:v>빈 Note 영역의 테두리만 제거하고 고정 템플릿 테두리는 보존</x:v>
-      </x:c>
-      <x:c r="K77" s="11" t="str">
-        <x:v>없음</x:v>
-      </x:c>
-      <x:c r="L77" s="11" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M77" s="11" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="N77" s="53" t="n">
+      <x:c r="B77" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C77" s="11" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D77" s="12" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G77" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H77" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I77" s="11" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J77" s="12" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="K77" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="L77" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M77" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N77" s="14">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="O77" s="53" t="n">
+      <x:c r="O77" s="14">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="P77" s="53" t="n">
+      <x:c r="P77" s="14">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="Q77" s="12" t="str">
-        <x:v>API 수정본 적용 후 빈 Note 영역 테두리 제거와 고정 템플릿 테두리 보존 확인 완료</x:v>
+      <x:c r="Q77" s="12" t="s">
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
@@ -6715,40 +6807,40 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>320</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="D78" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="E78" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F78" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G78" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H78" t="s">
-        <x:v>50</x:v>
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="E78" s="16" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F78" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G78" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H78" s="16" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I78" s="16" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J78" t="s">
-        <x:v>322</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="K78" t="s">
-        <x:v>305</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="L78" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M78" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N78" s="15"/>
       <x:c r="O78" s="15"/>
@@ -6756,7 +6848,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q78" t="s">
-        <x:v>323</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
@@ -6764,40 +6856,40 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>320</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="D79" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="E79" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F79" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G79" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H79" t="s">
-        <x:v>50</x:v>
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="E79" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F79" s="16" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G79" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H79" s="16" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I79" s="16" t="s">
-        <x:v>303</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J79" t="s">
-        <x:v>325</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="K79" t="s">
-        <x:v>310</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="L79" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M79" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="N79" s="15"/>
       <x:c r="O79" s="15"/>
@@ -6805,7 +6897,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q79" t="s">
-        <x:v>326</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6918,7 +7010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19fbd5588a824e72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R061e042e24a64541"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6937,19 +7029,19 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="B1" s="23"/>
-      <x:c r="C1" s="23"/>
-      <x:c r="D1" s="23"/>
-      <x:c r="E1" s="23"/>
-      <x:c r="F1" s="23"/>
-      <x:c r="G1" s="23"/>
+      <x:c r="A1" s="21" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B1" s="21"/>
+      <x:c r="C1" s="21"/>
+      <x:c r="D1" s="21"/>
+      <x:c r="E1" s="21"/>
+      <x:c r="F1" s="21"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="51" t="s">
-        <x:v>328</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B2" s="51"/>
       <x:c r="C2" s="51"/>
@@ -6960,7 +7052,7 @@
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="52" t="s">
-        <x:v>329</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B4" s="52"/>
       <x:c r="C4" s="52"/>
@@ -6971,122 +7063,122 @@
     </x:row>
     <x:row r="5" ht="37.95000076293945" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>330</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>331</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>332</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>333</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F5" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>334</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>335</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>336</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>337</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>338</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>339</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>340</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>341</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>342</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>343</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>344</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>345</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>346</x:v>
+        <x:v>378</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>347</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>348</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>349</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>350</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="52" t="s">
-        <x:v>351</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B11" s="52"/>
       <x:c r="C11" s="52"/>
@@ -7097,214 +7189,214 @@
     </x:row>
     <x:row r="12" ht="37.95000076293945" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>352</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>353</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>354</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F12" s="2" t="s">
-        <x:v>355</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>356</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>357</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>358</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>359</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>360</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>361</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>362</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>363</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>363</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>364</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>365</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
-        <x:v>366</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>367</x:v>
+        <x:v>399</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="3" t="s">
-        <x:v>266</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>369</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>370</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>372</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="36" customHeight="1">
       <x:c r="A18" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>373</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>374</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>375</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>376</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>377</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>372</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="36" customHeight="1">
       <x:c r="A20" s="3" t="s">
-        <x:v>273</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>378</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>377</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>372</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" customHeight="1">
       <x:c r="A22" s="52" t="s">
-        <x:v>379</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B22" s="52"/>
       <x:c r="C22" s="52"/>
@@ -7318,280 +7410,280 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>380</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>381</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>355</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>334</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
       <x:c r="A24" s="3" t="s">
-        <x:v>382</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>288</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>383</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>384</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>385</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="36" customHeight="1">
       <x:c r="A25" s="3" t="s">
-        <x:v>386</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>388</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>389</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="36" customHeight="1">
       <x:c r="A26" s="3" t="s">
-        <x:v>390</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>391</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>392</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="36" customHeight="1">
       <x:c r="A27" s="3" t="s">
-        <x:v>393</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>394</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>395</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="G27" s="3" t="str">
-        <x:v>빈 Note 영역 테두리 선택 제거 API 해결 완료. 입력 UI·긴 텍스트 정책은 별도 개발 필요</x:v>
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="s">
+        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="36" customHeight="1">
       <x:c r="A28" s="3" t="s">
-        <x:v>396</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>397</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>398</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>399</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="36" customHeight="1">
       <x:c r="A29" s="3" t="s">
-        <x:v>400</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>401</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>402</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>403</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="36" customHeight="1">
       <x:c r="A30" s="3" t="s">
-        <x:v>404</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>405</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>406</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>403</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="36" customHeight="1">
       <x:c r="A31" s="3" t="s">
-        <x:v>407</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>408</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>409</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
-        <x:v>410</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>411</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="36" customHeight="1">
       <x:c r="A32" s="3" t="s">
-        <x:v>283</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>412</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>413</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>414</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>415</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>416</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
-        <x:v>417</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="3" t="s">
-        <x:v>418</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>419</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>420</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="41" t="s">
-        <x:v>421</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B36" s="41"/>
       <x:c r="C36" s="41"/>
@@ -7605,142 +7697,142 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B37" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
-        <x:v>422</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="E37" s="6" t="s">
-        <x:v>423</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F37" s="6" t="s">
-        <x:v>355</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="G37" s="6" t="s">
-        <x:v>356</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="7" t="s">
-        <x:v>424</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B38" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C38" s="7" t="s">
-        <x:v>263</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
-        <x:v>425</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E38" s="7" t="s">
-        <x:v>426</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F38" s="7" t="s">
-        <x:v>371</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G38" s="7" t="s">
-        <x:v>427</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="7" t="s">
-        <x:v>428</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B39" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C39" s="7" t="s">
-        <x:v>61</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D39" s="7" t="s">
-        <x:v>429</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E39" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F39" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G39" s="7" t="s">
-        <x:v>430</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="36" customHeight="1">
       <x:c r="A40" s="7" t="s">
-        <x:v>431</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B40" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C40" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D40" s="7" t="s">
-        <x:v>432</x:v>
+      <x:c r="D40" s="7" t="str">
+        <x:v>진입 시 Measure·ShapeDrawing과 3D Review Note 정리</x:v>
       </x:c>
       <x:c r="E40" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F40" s="7" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G40" s="7" t="s">
-        <x:v>433</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>ISO 잔류 치수와 가공도 3D 미리보기 풍선 정리 완료. PDF 풍선 유지 실기 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="36" customHeight="1">
       <x:c r="A41" s="7" t="s">
-        <x:v>434</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B41" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C41" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="7" t="s">
-        <x:v>435</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E41" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F41" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G41" s="7" t="s">
-        <x:v>436</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" t="s">
-        <x:v>437</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D42" t="s">
-        <x:v>438</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E42" t="s">
-        <x:v>439</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F42" t="s">
-        <x:v>300</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="G42" t="s">
-        <x:v>440</x:v>
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="25.950000762939453" customHeight="1">
       <x:c r="A43" s="42" t="s">
-        <x:v>441</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B43" s="43"/>
       <x:c r="C43" s="43"/>
@@ -7751,7 +7843,7 @@
     </x:row>
     <x:row r="44" ht="25.950000762939453" customHeight="1">
       <x:c r="A44" s="45" t="s">
-        <x:v>442</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B44" s="46"/>
       <x:c r="C44" s="46"/>
@@ -7762,7 +7854,7 @@
     </x:row>
     <x:row r="45" ht="25.950000762939453" customHeight="1">
       <x:c r="A45" s="48" t="s">
-        <x:v>443</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B45" s="49"/>
       <x:c r="C45" s="49"/>

--- a/2D 자동 제작도 개발 현황.xlsx
+++ b/2D 자동 제작도 개발 현황.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="Re18135f7cc0d4a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="R90f8d174701f49ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="R6df1991648154a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="R9eed27be84864170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="R6b4d149df13a4f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="R0727e455856b4208"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1027,7 +1027,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="50">
+  <x:dxfs count="56">
     <x:dxf/>
     <x:dxf/>
     <x:dxf/>
@@ -1378,6 +1378,72 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF8CBAD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF222222"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
@@ -1995,7 +2061,7 @@
         <x:v>제작·가공·설치도 최종 PDF와 설명 장표</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>개발 대기</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>과제 완료 기준</x:v>
@@ -6046,7 +6112,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="I77" s="50" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>개발 대기</x:v>
       </x:c>
       <x:c r="J77" s="51" t="str">
         <x:v>제작도·가공도·설치도 최종 PDF와 메뉴얼·룰북 설명 장표 필요</x:v>
@@ -6097,7 +6163,7 @@
         <x:v>해당없음</x:v>
       </x:c>
       <x:c r="I78" s="50" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>개발 대기</x:v>
       </x:c>
       <x:c r="J78" s="51" t="str">
         <x:v>왼쪽 탭·테이블과 STRU 검색 상자의 배치·가독성 개선 필요</x:v>
@@ -6817,22 +6883,22 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="I6:I90">
-    <x:cfRule type="expression" dxfId="44" priority="28">
+    <x:cfRule type="expression" dxfId="50" priority="28">
       <x:formula>$I6="완료"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="45" priority="29">
+    <x:cfRule type="expression" dxfId="51" priority="29">
       <x:formula>$I6="실기 검증 대기"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="46" priority="30">
+    <x:cfRule type="expression" dxfId="52" priority="30">
       <x:formula>OR($I6="부분 구현",$I6="개발 중")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="47" priority="31">
+    <x:cfRule type="expression" dxfId="53" priority="31">
       <x:formula>OR($I6="개발 필요",$I6="개발 대기")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="48" priority="32">
+    <x:cfRule type="expression" dxfId="54" priority="32">
       <x:formula>OR($I6="분석 필요",$I6="적용 제외")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="49" priority="33">
+    <x:cfRule type="expression" dxfId="55" priority="33">
       <x:formula>OR($I6="출력 불가",$I6="API 요청 필요",$I6="API 대기")</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -6861,7 +6927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2729326ffcea4f3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39b817ca4fc743f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/2D 자동 제작도 개발 현황.xlsx
+++ b/2D 자동 제작도 개발 현황.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="R9eed27be84864170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="R6b4d149df13a4f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="R0727e455856b4208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황 요약" sheetId="1" r:id="R3a212f98f3334b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 항목" sheetId="2" r:id="Rf18a5700e6224d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항·UDA" sheetId="3" r:id="Reb403e87cc2343b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1027,7 +1027,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="56">
+  <x:dxfs count="68">
     <x:dxf/>
     <x:dxf/>
     <x:dxf/>
@@ -1444,6 +1444,138 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF8CBAD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF222222"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF8CBAD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF222222"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
@@ -1798,17 +1930,17 @@
       <x:c r="B5" s="17"/>
       <x:c r="C5" s="16" t="n">
         <x:f>COUNTIF('개발 항목'!$I$6:$I$90,"완료")</x:f>
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="17"/>
       <x:c r="E5" s="16" t="n">
         <x:f>COUNTIF('개발 항목'!$I$6:$I$90,"실기 검증 대기")</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="17"/>
       <x:c r="G5" s="16" t="n">
         <x:f>COUNTIFS('개발 항목'!$E$6:$E$90,"○",'개발 항목'!$H$6:$H$90,"&lt;&gt;O")</x:f>
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H5" s="17"/>
     </x:row>
@@ -1902,10 +2034,10 @@
         <x:v>가공도</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>EA 두 뷰 배율·치수·풍선 종이 정규화</x:v>
+        <x:v>치수·풍선 종이 절대 정규화</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>실기 검증 대기</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>가공 치수·표현 일관성</x:v>
@@ -1954,7 +2086,7 @@
         <x:v>제작도</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>ReferenceAxis 치수 문자 각도</x:v>
+        <x:v>UserAxis 치수 문자 각도</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>API 대기</x:v>
@@ -1966,10 +2098,10 @@
         <x:v>화면 수평 고정 또는 회전각 API 대기</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>UserAxis 문자</x:v>
+        <x:v>문자 각도만</x:v>
       </x:c>
       <x:c r="H13" s="54" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -2035,13 +2167,13 @@
         <x:v>취소 응답성·진행률·대규모 대상 경고</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>실기 검증 대기</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
         <x:v>장시간 작업 중단 불가</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>BOM 반복 확인 지점과 진행률 구현</x:v>
+        <x:v>대용량 모델 취소 반응·정리 동작 확인</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>취소 확인 지점</x:v>
@@ -2058,33 +2190,49 @@
         <x:v>최종</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
-        <x:v>제작·가공·설치도 최종 PDF와 설명 장표</x:v>
+        <x:v>제작·가공·설치도 최종 PDF와 설명 자료</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>개발 대기</x:v>
+        <x:v>개발 중</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>과제 완료 기준</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>메뉴얼·룰북 및 3종 생산 PDF 확정</x:v>
+        <x:v>메뉴얼·룰북 및 3종 생산 PDF 생성</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>도면·장표 산출물</x:v>
+        <x:v>도면·자료 산출물</x:v>
       </x:c>
       <x:c r="H17" s="54" t="n">
         <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="7"/>
-      <x:c r="C18" s="7"/>
-      <x:c r="D18" s="8"/>
-      <x:c r="E18" s="7"/>
-      <x:c r="F18" s="7"/>
-      <x:c r="G18" s="7"/>
-      <x:c r="H18" s="54"/>
+      <x:c r="A18" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>가공도</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="str">
+        <x:v>모떼기·라운드 형상 검출·표시</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>API 대기</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>가공 형상정보 누락</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="str">
+        <x:v>필터링 조건 정리와 8월 API 배포 대기</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>형상 검출 API</x:v>
+      </x:c>
+      <x:c r="H18" s="54" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19"/>
@@ -5016,16 +5164,16 @@
     </x:row>
     <x:row r="56" ht="42" hidden="0" customHeight="1">
       <x:c r="A56" s="48" t="n">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B56" s="48" t="str">
-        <x:v>설치도</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C56" s="48" t="str">
-        <x:v>ISO 표현</x:v>
+        <x:v>레이아웃·표현</x:v>
       </x:c>
       <x:c r="D56" s="10" t="str">
-        <x:v>도면 연결부재·외부 Assembly 표시</x:v>
+        <x:v>가공도 EA 두 뷰 배율·표현 일관성</x:v>
       </x:c>
       <x:c r="E56" s="48" t="str">
         <x:v>○</x:v>
@@ -5037,13 +5185,13 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="H56" s="48" t="str">
-        <x:v>대기</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="I56" s="48" t="str">
-        <x:v>실기 검증 대기</x:v>
+        <x:v>완료</x:v>
       </x:c>
       <x:c r="J56" s="10" t="str">
-        <x:v>InstallationContextIndices + LONG_DASHED</x:v>
+        <x:v>EA 두 뷰 배율·길이·두께 표현 일관성 보정 완료</x:v>
       </x:c>
       <x:c r="K56" s="48" t="str">
         <x:v>없음</x:v>
@@ -5057,27 +5205,29 @@
       <x:c r="N56" s="53" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="O56" s="53"/>
+      <x:c r="O56" s="53" t="n">
+        <x:v>46227</x:v>
+      </x:c>
       <x:c r="P56" s="53" t="n">
-        <x:v>46224</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q56" s="10" t="str">
-        <x:v>4개 뷰 코드 반영, 실기 PDF 대기</x:v>
+        <x:v>GitHub 종료 기준 완료 반영. 치수·풍선 종이 절대 정규화 실기는 별도 항목으로 관리</x:v>
       </x:c>
       <x:c r="R56"/>
     </x:row>
     <x:row r="57" ht="42" hidden="0" customHeight="1">
       <x:c r="A57" s="48" t="n">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B57" s="48" t="str">
-        <x:v>가공도</x:v>
+        <x:v>설치도</x:v>
       </x:c>
       <x:c r="C57" s="48" t="str">
-        <x:v>레이아웃</x:v>
+        <x:v>ISO 표현</x:v>
       </x:c>
       <x:c r="D57" s="10" t="str">
-        <x:v>가공도 EA 상하 2뷰 배치</x:v>
+        <x:v>도면 연결부재·외부 Assembly 표시</x:v>
       </x:c>
       <x:c r="E57" s="48" t="str">
         <x:v>○</x:v>
@@ -5086,50 +5236,50 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="G57" s="48" t="str">
-        <x:v>△</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="H57" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>대기</x:v>
       </x:c>
       <x:c r="I57" s="48" t="str">
-        <x:v>분석 필요</x:v>
+        <x:v>실기 검증 대기</x:v>
       </x:c>
       <x:c r="J57" s="10" t="str">
-        <x:v>EA 두 뷰는 있으나 앵글 형강의 촬영 기준면·방향 규칙이 미확정</x:v>
+        <x:v>InstallationContextIndices + LONG_DASHED</x:v>
       </x:c>
       <x:c r="K57" s="48" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>없음</x:v>
       </x:c>
       <x:c r="L57" s="48" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="M57" s="48" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="N57" s="53" t="n">
-        <x:v>46188</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="O57" s="53"/>
       <x:c r="P57" s="53" t="n">
-        <x:v>46227</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="Q57" s="10" t="str">
-        <x:v>앵글 형강 열린 방향과 미러·뷰 교환 기준을 먼저 확정해야 함</x:v>
+        <x:v>4개 뷰 코드 반영, 실기 PDF 대기</x:v>
       </x:c>
       <x:c r="R57"/>
     </x:row>
     <x:row r="58" ht="42" hidden="0" customHeight="1">
       <x:c r="A58" s="48" t="n">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B58" s="48" t="str">
-        <x:v>제작·조립·설치·가공</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C58" s="48" t="str">
-        <x:v>표제부</x:v>
+        <x:v>치수·풍선</x:v>
       </x:c>
       <x:c r="D58" s="10" t="str">
-        <x:v>긴 Note 처리 정책</x:v>
+        <x:v>치수·풍선 크기 종이 절대 정규화</x:v>
       </x:c>
       <x:c r="E58" s="48" t="str">
         <x:v>○</x:v>
@@ -5138,98 +5288,102 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="G58" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="H58" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>대기</x:v>
       </x:c>
       <x:c r="I58" s="48" t="str">
-        <x:v>분석 필요</x:v>
+        <x:v>실기 검증 대기</x:v>
       </x:c>
       <x:c r="J58" s="10" t="str">
-        <x:v>고정 크기 Note 박스</x:v>
+        <x:v>캔버스 절대 크기 기준 구현과 Debug·Release 빌드 완료</x:v>
       </x:c>
       <x:c r="K58" s="48" t="str">
-        <x:v>사양/API 확인</x:v>
+        <x:v>실기 확인</x:v>
       </x:c>
       <x:c r="L58" s="48" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="M58" s="48" t="str">
         <x:v>O</x:v>
       </x:c>
-      <x:c r="N58" s="53"/>
+      <x:c r="N58" s="53" t="n">
+        <x:v>46226</x:v>
+      </x:c>
       <x:c r="O58" s="53"/>
       <x:c r="P58" s="53" t="n">
-        <x:v>46224</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q58" s="10" t="str">
-        <x:v>글자 제한·말줄임·폰트 축소 중 정책 결정 필요</x:v>
+        <x:v>크기 차가 큰 부재 혼합 페이지에서 치수·풍선 종이 크기 일관성 확인 대기</x:v>
       </x:c>
       <x:c r="R58"/>
     </x:row>
     <x:row r="59" ht="42" hidden="0" customHeight="1">
       <x:c r="A59" s="48" t="n">
-        <x:v>54</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B59" s="48" t="str">
-        <x:v>가공도</x:v>
+        <x:v>공통</x:v>
       </x:c>
       <x:c r="C59" s="48" t="str">
-        <x:v>형상</x:v>
+        <x:v>자동화 UX</x:v>
       </x:c>
       <x:c r="D59" s="10" t="str">
-        <x:v>라운드 표시</x:v>
+        <x:v>치수 추출·도면 출력 취소 응답성·진행률</x:v>
       </x:c>
       <x:c r="E59" s="48" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="F59" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="G59" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="H59" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>해당없음</x:v>
       </x:c>
       <x:c r="I59" s="48" t="str">
-        <x:v>분석 필요</x:v>
+        <x:v>실기 검증 대기</x:v>
       </x:c>
       <x:c r="J59" s="10" t="str">
-        <x:v>사용 가능한 SDK API 미확인</x:v>
+        <x:v>BOM 반복 취소·진행률·대규모 대상 경고 구현과 빌드 완료</x:v>
       </x:c>
       <x:c r="K59" s="48" t="str">
-        <x:v>API/분석</x:v>
+        <x:v>실기 확인</x:v>
       </x:c>
       <x:c r="L59" s="48" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="M59" s="48" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N59" s="53"/>
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="N59" s="53" t="n">
+        <x:v>46226</x:v>
+      </x:c>
       <x:c r="O59" s="53"/>
       <x:c r="P59" s="53" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q59" s="10" t="str">
-        <x:v>라운드·필렛 판정 기준과 필터 조건을 정한 뒤 8월 API 요청 여부 결정</x:v>
+        <x:v>대용량 모델에서 취소 반응 속도와 부분 결과 정리 동작 확인 대기</x:v>
       </x:c>
       <x:c r="R59"/>
     </x:row>
     <x:row r="60" ht="42" hidden="0" customHeight="1">
       <x:c r="A60" s="48" t="n">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B60" s="48" t="str">
         <x:v>가공도</x:v>
       </x:c>
       <x:c r="C60" s="48" t="str">
-        <x:v>형상</x:v>
+        <x:v>레이아웃</x:v>
       </x:c>
       <x:c r="D60" s="10" t="str">
-        <x:v>모떼기(챔퍼) 표현</x:v>
+        <x:v>가공도 EA 상하 2뷰 배치</x:v>
       </x:c>
       <x:c r="E60" s="48" t="str">
         <x:v>○</x:v>
@@ -5238,7 +5392,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="G60" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>△</x:v>
       </x:c>
       <x:c r="H60" s="48" t="str">
         <x:v>X</x:v>
@@ -5247,30 +5401,32 @@
         <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J60" s="10" t="str">
-        <x:v>추출 방법 미정</x:v>
+        <x:v>EA 두 뷰는 있으나 앵글 형강의 촬영 기준면·방향 규칙이 미확정</x:v>
       </x:c>
       <x:c r="K60" s="48" t="str">
-        <x:v>API/분석</x:v>
+        <x:v>앱 개발</x:v>
       </x:c>
       <x:c r="L60" s="48" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M60" s="48" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N60" s="53"/>
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="N60" s="53" t="n">
+        <x:v>46188</x:v>
+      </x:c>
       <x:c r="O60" s="53"/>
       <x:c r="P60" s="53" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q60" s="10" t="str">
-        <x:v>모떼기 판정 기준과 필터 조건을 정한 뒤 8월 API 요청 여부 결정</x:v>
+        <x:v>앵글 형강 열린 방향과 미러·뷰 교환 기준을 먼저 확정해야 함</x:v>
       </x:c>
       <x:c r="R60"/>
     </x:row>
     <x:row r="61" ht="42" hidden="0" customHeight="1">
       <x:c r="A61" s="8" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B61" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5279,10 +5435,10 @@
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D61" s="7" t="str">
-        <x:v>Grinding / Welding 공법 표시</x:v>
+        <x:v>긴 Note 처리 정책</x:v>
       </x:c>
       <x:c r="E61" s="8" t="str">
-        <x:v>△</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="F61" s="8" t="str">
         <x:v>X</x:v>
@@ -5297,45 +5453,45 @@
         <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J61" s="7" t="str">
-        <x:v>현재 값 연결 없음</x:v>
+        <x:v>고정 크기 Note 박스</x:v>
       </x:c>
       <x:c r="K61" s="8" t="str">
-        <x:v>UDA/업무 규칙</x:v>
+        <x:v>사양/API 확인</x:v>
       </x:c>
       <x:c r="L61" s="8" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M61" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="N61" s="54"/>
       <x:c r="O61" s="54"/>
       <x:c r="P61" s="54" t="n">
-        <x:v>46225</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="Q61" s="7" t="str">
-        <x:v>부재별/도면별 공법 데이터 위치 확인 필요</x:v>
+        <x:v>글자 제한·말줄임·폰트 축소 중 정책 결정 필요</x:v>
       </x:c>
       <x:c r="R61"/>
     </x:row>
     <x:row r="62" ht="42" hidden="0" customHeight="1">
       <x:c r="A62" s="48" t="n">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B62" s="48" t="str">
-        <x:v>가공도</x:v>
+        <x:v>제작·조립·설치·가공</x:v>
       </x:c>
       <x:c r="C62" s="48" t="str">
-        <x:v>치수 디자인</x:v>
+        <x:v>표제부</x:v>
       </x:c>
       <x:c r="D62" s="10" t="str">
-        <x:v>가공도 텍스트-모델 충돌</x:v>
+        <x:v>Grinding / Welding 공법 표시</x:v>
       </x:c>
       <x:c r="E62" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>△</x:v>
       </x:c>
       <x:c r="F62" s="48" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="G62" s="48" t="str">
         <x:v>X</x:v>
@@ -5347,10 +5503,10 @@
         <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J62" s="10" t="str">
-        <x:v>배치 충돌 판정 없음</x:v>
+        <x:v>현재 값 연결 없음</x:v>
       </x:c>
       <x:c r="K62" s="48" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>UDA/업무 규칙</x:v>
       </x:c>
       <x:c r="L62" s="48" t="str">
         <x:v>O</x:v>
@@ -5361,31 +5517,31 @@
       <x:c r="N62" s="53"/>
       <x:c r="O62" s="53"/>
       <x:c r="P62" s="53" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="Q62" s="10" t="str">
-        <x:v>생산 정보 자체보다 가독성 디자인 항목</x:v>
+        <x:v>부재별/도면별 공법 데이터 위치 확인 필요</x:v>
       </x:c>
       <x:c r="R62"/>
     </x:row>
     <x:row r="63" ht="42" hidden="0" customHeight="1">
       <x:c r="A63" s="48" t="n">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B63" s="48" t="str">
-        <x:v>공통</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C63" s="48" t="str">
-        <x:v>출력 파일명</x:v>
+        <x:v>치수 디자인</x:v>
       </x:c>
       <x:c r="D63" s="10" t="str">
-        <x:v>자동 저장 PDF 파일명 정규화</x:v>
+        <x:v>가공도 텍스트-모델 충돌</x:v>
       </x:c>
       <x:c r="E63" s="48" t="str">
-        <x:v>△</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="F63" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="G63" s="48" t="str">
         <x:v>X</x:v>
@@ -5397,7 +5553,7 @@
         <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J63" s="10" t="str">
-        <x:v>도면 종류별 자동 저장 경로와 파일명 규칙이 일관되지 않음</x:v>
+        <x:v>배치 충돌 판정 없음</x:v>
       </x:c>
       <x:c r="K63" s="48" t="str">
         <x:v>앱 개발</x:v>
@@ -5406,41 +5562,39 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="M63" s="48" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="N63" s="53" t="n">
-        <x:v>46227</x:v>
-      </x:c>
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N63" s="53"/>
       <x:c r="O63" s="53"/>
       <x:c r="P63" s="53" t="n">
-        <x:v>46227</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="Q63" s="10" t="str">
-        <x:v>프로젝트·TAG·도면 종류·개정 번호를 포함할지 명명 규칙 확정 필요</x:v>
+        <x:v>생산 정보 자체보다 가독성 디자인 항목</x:v>
       </x:c>
       <x:c r="R63"/>
     </x:row>
     <x:row r="64" ht="42" hidden="0" customHeight="1">
       <x:c r="A64" s="48" t="n">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B64" s="48" t="str">
-        <x:v>가공도</x:v>
+        <x:v>공통</x:v>
       </x:c>
       <x:c r="C64" s="48" t="str">
-        <x:v>촬영 방향</x:v>
+        <x:v>출력 파일명</x:v>
       </x:c>
       <x:c r="D64" s="10" t="str">
-        <x:v>앵글(ㄱ자) 형강 촬영 방향 기준</x:v>
+        <x:v>자동 저장 PDF 파일명 정규화</x:v>
       </x:c>
       <x:c r="E64" s="48" t="str">
-        <x:v>○</x:v>
+        <x:v>△</x:v>
       </x:c>
       <x:c r="F64" s="48" t="str">
         <x:v>X</x:v>
       </x:c>
       <x:c r="G64" s="48" t="str">
-        <x:v>△</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="H64" s="48" t="str">
         <x:v>X</x:v>
@@ -5449,7 +5603,7 @@
         <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J64" s="10" t="str">
-        <x:v>주·보조 카메라가 X_PLUS·Z_MINUS로 고정돼 앵글 열린 방향을 반영하지 못함</x:v>
+        <x:v>도면 종류별 자동 저장 경로와 파일명 규칙이 일관되지 않음</x:v>
       </x:c>
       <x:c r="K64" s="48" t="str">
         <x:v>앱 개발</x:v>
@@ -5468,22 +5622,22 @@
         <x:v>46227</x:v>
       </x:c>
       <x:c r="Q64" s="10" t="str">
-        <x:v>기준면·열린 방향·미러와 두 뷰 교환 정책을 먼저 확정해야 함</x:v>
+        <x:v>프로젝트·TAG·도면 종류·개정 번호를 포함할지 명명 규칙 확정 필요</x:v>
       </x:c>
       <x:c r="R64"/>
     </x:row>
     <x:row r="65" ht="42" hidden="0" customHeight="1">
       <x:c r="A65" s="48" t="n">
-        <x:v>26</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B65" s="48" t="str">
-        <x:v>제작·조립·설치·가공</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C65" s="48" t="str">
-        <x:v>BOM</x:v>
+        <x:v>촬영 방향</x:v>
       </x:c>
       <x:c r="D65" s="10" t="str">
-        <x:v>SIZE</x:v>
+        <x:v>앵글(ㄱ자) 형강 촬영 방향 기준</x:v>
       </x:c>
       <x:c r="E65" s="48" t="str">
         <x:v>○</x:v>
@@ -5495,47 +5649,47 @@
         <x:v>△</x:v>
       </x:c>
       <x:c r="H65" s="48" t="str">
-        <x:v>대기</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="I65" s="48" t="str">
-        <x:v>부분 구현</x:v>
+        <x:v>분석 필요</x:v>
       </x:c>
       <x:c r="J65" s="10" t="str">
-        <x:v>SPREF 나머지 + POSSTART/POSEND 3D 거리</x:v>
+        <x:v>주·보조 카메라가 X_PLUS·Z_MINUS로 고정돼 앵글 열린 방향을 반영하지 못함</x:v>
       </x:c>
       <x:c r="K65" s="48" t="str">
-        <x:v>UDA/규칙 확정</x:v>
+        <x:v>앱 개발</x:v>
       </x:c>
       <x:c r="L65" s="48" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M65" s="48" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="N65" s="53" t="n">
-        <x:v>46155</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="O65" s="53"/>
       <x:c r="P65" s="53" t="n">
-        <x:v>46155</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q65" s="10" t="str">
-        <x:v>현재 숫자 토큰 순서 가정; 생산 형식 검증 필요</x:v>
+        <x:v>기준면·열린 방향·미러와 두 뷰 교환 정책을 먼저 확정해야 함</x:v>
       </x:c>
       <x:c r="R65"/>
     </x:row>
     <x:row r="66" ht="42" hidden="0" customHeight="1">
       <x:c r="A66" s="8" t="n">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B66" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
       </x:c>
       <x:c r="C66" s="8" t="str">
-        <x:v>표제부</x:v>
+        <x:v>BOM</x:v>
       </x:c>
       <x:c r="D66" s="7" t="str">
-        <x:v>프로젝트명</x:v>
+        <x:v>SIZE</x:v>
       </x:c>
       <x:c r="E66" s="8" t="str">
         <x:v>○</x:v>
@@ -5547,16 +5701,16 @@
         <x:v>△</x:v>
       </x:c>
       <x:c r="H66" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>대기</x:v>
       </x:c>
       <x:c r="I66" s="8" t="str">
         <x:v>부분 구현</x:v>
       </x:c>
       <x:c r="J66" s="7" t="str">
-        <x:v>현재 CEDAR FLNG 하드코딩</x:v>
+        <x:v>SPREF 나머지 + POSSTART/POSEND 3D 거리</x:v>
       </x:c>
       <x:c r="K66" s="8" t="str">
-        <x:v>데이터 연결</x:v>
+        <x:v>UDA/규칙 확정</x:v>
       </x:c>
       <x:c r="L66" s="8" t="str">
         <x:v>O</x:v>
@@ -5565,20 +5719,20 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="N66" s="54" t="n">
-        <x:v>46156</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="O66" s="54"/>
       <x:c r="P66" s="54" t="n">
-        <x:v>46225</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="Q66" s="7" t="str">
-        <x:v>프로젝트 메타 또는 UDA 연결 필요</x:v>
+        <x:v>현재 숫자 토큰 순서 가정; 생산 형식 검증 필요</x:v>
       </x:c>
       <x:c r="R66"/>
     </x:row>
     <x:row r="67" ht="42" hidden="0" customHeight="1">
       <x:c r="A67" s="8" t="n">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B67" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5587,7 +5741,7 @@
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D67" s="7" t="str">
-        <x:v>선박번호 / Project No</x:v>
+        <x:v>프로젝트명</x:v>
       </x:c>
       <x:c r="E67" s="8" t="str">
         <x:v>○</x:v>
@@ -5605,7 +5759,7 @@
         <x:v>부분 구현</x:v>
       </x:c>
       <x:c r="J67" s="7" t="str">
-        <x:v>현재 SN2688 하드코딩</x:v>
+        <x:v>현재 CEDAR FLNG 하드코딩</x:v>
       </x:c>
       <x:c r="K67" s="8" t="str">
         <x:v>데이터 연결</x:v>
@@ -5624,22 +5778,22 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q67" s="7" t="str">
-        <x:v>정식 필드명과 데이터 소스 확정 필요</x:v>
+        <x:v>프로젝트 메타 또는 UDA 연결 필요</x:v>
       </x:c>
       <x:c r="R67"/>
     </x:row>
     <x:row r="68" ht="42" hidden="0" customHeight="1">
       <x:c r="A68" s="8" t="n">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B68" s="8" t="str">
-        <x:v>제작·조립·설치</x:v>
+        <x:v>제작·조립·설치·가공</x:v>
       </x:c>
       <x:c r="C68" s="8" t="str">
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D68" s="7" t="str">
-        <x:v>Tag No</x:v>
+        <x:v>선박번호 / Project No</x:v>
       </x:c>
       <x:c r="E68" s="8" t="str">
         <x:v>○</x:v>
@@ -5651,55 +5805,53 @@
         <x:v>△</x:v>
       </x:c>
       <x:c r="H68" s="8" t="str">
-        <x:v>대기</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="I68" s="8" t="str">
         <x:v>부분 구현</x:v>
       </x:c>
       <x:c r="J68" s="7" t="str">
-        <x:v>조상 UDA STRU → Input 169</x:v>
+        <x:v>현재 SN2688 하드코딩</x:v>
       </x:c>
       <x:c r="K68" s="8" t="str">
-        <x:v>앱 보강</x:v>
+        <x:v>데이터 연결</x:v>
       </x:c>
       <x:c r="L68" s="8" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M68" s="8" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="N68" s="54" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="O68" s="54" t="n">
-        <x:v>46225</x:v>
-      </x:c>
+        <x:v>46156</x:v>
+      </x:c>
+      <x:c r="O68" s="54"/>
       <x:c r="P68" s="54" t="n">
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q68" s="7" t="str">
-        <x:v>테스트 케이스 실기 완료; 음수 BaseMemberIndex 시 공백 가능</x:v>
+        <x:v>정식 필드명과 데이터 소스 확정 필요</x:v>
       </x:c>
       <x:c r="R68"/>
     </x:row>
     <x:row r="69" ht="42" hidden="0" customHeight="1">
       <x:c r="A69" s="8" t="n">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B69" s="8" t="str">
         <x:v>제작·조립·설치</x:v>
       </x:c>
       <x:c r="C69" s="8" t="str">
-        <x:v>이미지</x:v>
+        <x:v>표제부</x:v>
       </x:c>
       <x:c r="D69" s="7" t="str">
-        <x:v>고객·프로젝트 이미지</x:v>
+        <x:v>Tag No</x:v>
       </x:c>
       <x:c r="E69" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="F69" s="8" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="G69" s="8" t="str">
         <x:v>△</x:v>
@@ -5711,10 +5863,10 @@
         <x:v>부분 구현</x:v>
       </x:c>
       <x:c r="J69" s="7" t="str">
-        <x:v>{Image_4} + ClientTestImage.png</x:v>
+        <x:v>조상 UDA STRU → Input 169</x:v>
       </x:c>
       <x:c r="K69" s="8" t="str">
-        <x:v>데이터/파일 선택</x:v>
+        <x:v>앱 보강</x:v>
       </x:c>
       <x:c r="L69" s="8" t="str">
         <x:v>O</x:v>
@@ -5725,68 +5877,72 @@
       <x:c r="N69" s="54" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="O69" s="54"/>
+      <x:c r="O69" s="54" t="n">
+        <x:v>46225</x:v>
+      </x:c>
       <x:c r="P69" s="54" t="n">
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q69" s="7" t="str">
-        <x:v>테스트 이미지 고정, 프로젝트별 공급 방식 미구현</x:v>
+        <x:v>테스트 케이스 실기 완료; 음수 BaseMemberIndex 시 공백 가능</x:v>
       </x:c>
       <x:c r="R69"/>
     </x:row>
     <x:row r="70" ht="42" hidden="0" customHeight="1">
       <x:c r="A70" s="8" t="n">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B70" s="8" t="str">
-        <x:v>제작·조립·설치·가공</x:v>
+        <x:v>제작·조립·설치</x:v>
       </x:c>
       <x:c r="C70" s="8" t="str">
-        <x:v>BOM</x:v>
+        <x:v>이미지</x:v>
       </x:c>
       <x:c r="D70" s="7" t="str">
-        <x:v>Q'TY</x:v>
+        <x:v>고객·프로젝트 이미지</x:v>
       </x:c>
       <x:c r="E70" s="8" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="F70" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="G70" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>△</x:v>
       </x:c>
       <x:c r="H70" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>대기</x:v>
       </x:c>
       <x:c r="I70" s="8" t="str">
-        <x:v>개발 필요</x:v>
+        <x:v>부분 구현</x:v>
       </x:c>
       <x:c r="J70" s="7" t="str">
-        <x:v>현재 항상 1</x:v>
+        <x:v>{Image_4} + ClientTestImage.png</x:v>
       </x:c>
       <x:c r="K70" s="8" t="str">
-        <x:v>UDA/집계 규칙</x:v>
+        <x:v>데이터/파일 선택</x:v>
       </x:c>
       <x:c r="L70" s="8" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M70" s="8" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N70" s="54"/>
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="N70" s="54" t="n">
+        <x:v>46224</x:v>
+      </x:c>
       <x:c r="O70" s="54"/>
       <x:c r="P70" s="54" t="n">
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q70" s="7" t="str">
-        <x:v>동일 부재 집계 또는 수량 UDA 정의 필요</x:v>
+        <x:v>테스트 이미지 고정, 프로젝트별 공급 방식 미구현</x:v>
       </x:c>
       <x:c r="R70"/>
     </x:row>
     <x:row r="71" ht="42" hidden="0" customHeight="1">
       <x:c r="A71" s="8" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B71" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5795,7 +5951,7 @@
         <x:v>BOM</x:v>
       </x:c>
       <x:c r="D71" s="7" t="str">
-        <x:v>MA</x:v>
+        <x:v>Q'TY</x:v>
       </x:c>
       <x:c r="E71" s="8" t="str">
         <x:v>○</x:v>
@@ -5813,10 +5969,10 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J71" s="7" t="str">
-        <x:v>현재 데이터행 L, 요약행 F 고정</x:v>
+        <x:v>현재 항상 1</x:v>
       </x:c>
       <x:c r="K71" s="8" t="str">
-        <x:v>UDA/업무 규칙</x:v>
+        <x:v>UDA/집계 규칙</x:v>
       </x:c>
       <x:c r="L71" s="8" t="str">
         <x:v>O</x:v>
@@ -5830,13 +5986,13 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q71" s="7" t="str">
-        <x:v>실제 의미와 데이터 원천 미정</x:v>
+        <x:v>동일 부재 집계 또는 수량 UDA 정의 필요</x:v>
       </x:c>
       <x:c r="R71"/>
     </x:row>
     <x:row r="72" ht="42" hidden="0" customHeight="1">
       <x:c r="A72" s="8" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B72" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5845,7 +6001,7 @@
         <x:v>BOM</x:v>
       </x:c>
       <x:c r="D72" s="7" t="str">
-        <x:v>FA</x:v>
+        <x:v>MA</x:v>
       </x:c>
       <x:c r="E72" s="8" t="str">
         <x:v>○</x:v>
@@ -5863,7 +6019,7 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J72" s="7" t="str">
-        <x:v>현재 항상 F</x:v>
+        <x:v>현재 데이터행 L, 요약행 F 고정</x:v>
       </x:c>
       <x:c r="K72" s="8" t="str">
         <x:v>UDA/업무 규칙</x:v>
@@ -5886,16 +6042,16 @@
     </x:row>
     <x:row r="73" ht="42" hidden="0" customHeight="1">
       <x:c r="A73" s="8" t="n">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B73" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
       </x:c>
       <x:c r="C73" s="8" t="str">
-        <x:v>표제부</x:v>
+        <x:v>BOM</x:v>
       </x:c>
       <x:c r="D73" s="7" t="str">
-        <x:v>PNOD / No Paint 표시</x:v>
+        <x:v>FA</x:v>
       </x:c>
       <x:c r="E73" s="8" t="str">
         <x:v>○</x:v>
@@ -5913,7 +6069,7 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J73" s="7" t="str">
-        <x:v>현재 값 연결 없음</x:v>
+        <x:v>현재 항상 F</x:v>
       </x:c>
       <x:c r="K73" s="8" t="str">
         <x:v>UDA/업무 규칙</x:v>
@@ -5930,12 +6086,12 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q73" s="7" t="str">
-        <x:v>기존 파일의 생산 필수 항목; Paint와 함께 정의 필요</x:v>
+        <x:v>실제 의미와 데이터 원천 미정</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="42" hidden="0" customHeight="1">
       <x:c r="A74" s="8" t="n">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B74" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5944,7 +6100,7 @@
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D74" s="7" t="str">
-        <x:v>Note 입력·저장·출력</x:v>
+        <x:v>PNOD / No Paint 표시</x:v>
       </x:c>
       <x:c r="E74" s="8" t="str">
         <x:v>○</x:v>
@@ -5962,31 +6118,29 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J74" s="7" t="str">
-        <x:v>Input 164/200 칸은 있으나 입력 소스 없음</x:v>
+        <x:v>현재 값 연결 없음</x:v>
       </x:c>
       <x:c r="K74" s="8" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>UDA/업무 규칙</x:v>
       </x:c>
       <x:c r="L74" s="8" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M74" s="8" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="N74" s="54" t="n">
-        <x:v>46213</x:v>
-      </x:c>
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N74" s="54"/>
       <x:c r="O74" s="54"/>
       <x:c r="P74" s="54" t="n">
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q74" s="7" t="str">
-        <x:v>UI·저장 모델·출력 배선이 모두 필요</x:v>
+        <x:v>기존 파일의 생산 필수 항목; Paint와 함께 정의 필요</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" hidden="0" customHeight="1">
       <x:c r="A75" s="8" t="n">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B75" s="8" t="str">
         <x:v>제작·조립·설치·가공</x:v>
@@ -5995,7 +6149,7 @@
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D75" s="7" t="str">
-        <x:v>Rev 입력·이력·출력</x:v>
+        <x:v>Note 입력·저장·출력</x:v>
       </x:c>
       <x:c r="E75" s="8" t="str">
         <x:v>○</x:v>
@@ -6013,7 +6167,7 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J75" s="7" t="str">
-        <x:v>Input 170~199 Rev 표 자리만 존재</x:v>
+        <x:v>Input 164/200 칸은 있으나 입력 소스 없음</x:v>
       </x:c>
       <x:c r="K75" s="8" t="str">
         <x:v>앱 개발</x:v>
@@ -6022,7 +6176,7 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="M75" s="8" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="N75" s="54" t="n">
         <x:v>46213</x:v>
@@ -6032,21 +6186,21 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q75" s="7" t="str">
-        <x:v>Revision 번호/일자/작성자/변경내용 규칙 필요</x:v>
+        <x:v>UI·저장 모델·출력 배선이 모두 필요</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="42" hidden="0" customHeight="1">
       <x:c r="A76" s="8" t="n">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B76" s="8" t="str">
-        <x:v>제작·조립·설치</x:v>
+        <x:v>제작·조립·설치·가공</x:v>
       </x:c>
       <x:c r="C76" s="8" t="str">
         <x:v>표제부</x:v>
       </x:c>
       <x:c r="D76" s="7" t="str">
-        <x:v>DP No</x:v>
+        <x:v>Rev 입력·이력·출력</x:v>
       </x:c>
       <x:c r="E76" s="8" t="str">
         <x:v>○</x:v>
@@ -6064,40 +6218,40 @@
         <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J76" s="7" t="str">
-        <x:v>현재 Test 하드코딩 → Input 168</x:v>
+        <x:v>Input 170~199 Rev 표 자리만 존재</x:v>
       </x:c>
       <x:c r="K76" s="8" t="str">
-        <x:v>UDA/데이터 연결</x:v>
+        <x:v>앱 개발</x:v>
       </x:c>
       <x:c r="L76" s="8" t="str">
         <x:v>O</x:v>
       </x:c>
       <x:c r="M76" s="8" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="N76" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="O76" s="54"/>
       <x:c r="P76" s="54" t="n">
         <x:v>46225</x:v>
       </x:c>
       <x:c r="Q76" s="7" t="str">
-        <x:v>Test 값 출력은 확인했지만 정식 생산 데이터 연결은 미완료</x:v>
+        <x:v>Revision 번호/일자/작성자/변경내용 규칙 필요</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" hidden="0" customHeight="1">
       <x:c r="A77" s="50" t="n">
-        <x:v>67</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B77" s="50" t="str">
-        <x:v>공통</x:v>
+        <x:v>제작·조립·설치</x:v>
       </x:c>
       <x:c r="C77" s="50" t="str">
-        <x:v>최종 산출물</x:v>
+        <x:v>표제부</x:v>
       </x:c>
       <x:c r="D77" s="51" t="str">
-        <x:v>제작도·가공도·설치도 최종 생산 출력</x:v>
+        <x:v>DP No</x:v>
       </x:c>
       <x:c r="E77" s="50" t="str">
         <x:v>○</x:v>
@@ -6106,19 +6260,19 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="G77" s="50" t="str">
-        <x:v>△</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="H77" s="50" t="str">
         <x:v>X</x:v>
       </x:c>
       <x:c r="I77" s="50" t="str">
-        <x:v>개발 대기</x:v>
+        <x:v>개발 필요</x:v>
       </x:c>
       <x:c r="J77" s="51" t="str">
-        <x:v>제작도·가공도·설치도 최종 PDF와 메뉴얼·룰북 설명 장표 필요</x:v>
+        <x:v>현재 Test 하드코딩 → Input 168</x:v>
       </x:c>
       <x:c r="K77" s="50" t="str">
-        <x:v>산출물 제작</x:v>
+        <x:v>UDA/데이터 연결</x:v>
       </x:c>
       <x:c r="L77" s="50" t="str">
         <x:v>O</x:v>
@@ -6127,14 +6281,14 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="N77" s="55" t="n">
-        <x:v>46155</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="O77" s="55"/>
       <x:c r="P77" s="55" t="n">
-        <x:v>46227</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="Q77" s="51" t="str">
-        <x:v>최종 생산 PDF 3종과 메뉴얼·룰북 구조의 설명 자료 및 프로젝트 이미지 확정 필요</x:v>
+        <x:v>Test 값 출력은 확인했지만 정식 생산 데이터 연결은 미완료</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" hidden="0" customHeight="1">
@@ -6188,16 +6342,16 @@
     </x:row>
     <x:row r="79" ht="42" hidden="0" customHeight="1">
       <x:c r="A79" s="50" t="n">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B79" s="50" t="str">
-        <x:v>가공도</x:v>
+        <x:v>공통</x:v>
       </x:c>
       <x:c r="C79" s="50" t="str">
-        <x:v>레이아웃·표현</x:v>
+        <x:v>최종 산출물</x:v>
       </x:c>
       <x:c r="D79" s="51" t="str">
-        <x:v>가공도 EA 두 뷰 배율·표현 일관성</x:v>
+        <x:v>제작도·가공도·설치도 최종 생산 출력</x:v>
       </x:c>
       <x:c r="E79" s="50" t="str">
         <x:v>○</x:v>
@@ -6215,10 +6369,10 @@
         <x:v>개발 중</x:v>
       </x:c>
       <x:c r="J79" s="51" t="str">
-        <x:v>풍선 영역은 해결됐으나 부재별 배율·길이·두께 표현이 일정하지 않음</x:v>
+        <x:v>제작도·가공도·설치도 최종 PDF와 메뉴얼·룰북 설명 자료 생성 중</x:v>
       </x:c>
       <x:c r="K79" s="50" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>산출물 생성</x:v>
       </x:c>
       <x:c r="L79" s="50" t="str">
         <x:v>O</x:v>
@@ -6227,79 +6381,77 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="N79" s="55" t="n">
-        <x:v>46224</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="O79" s="55"/>
       <x:c r="P79" s="55" t="n">
         <x:v>46227</x:v>
       </x:c>
       <x:c r="Q79" s="51" t="str">
-        <x:v>크기 차가 큰 부재를 같은 페이지에 배치해 종이 절대 크기 정규화를 개발 중</x:v>
+        <x:v>코드 개발보다 최종 생산 PDF·설명 자료·프로젝트 이미지 산출물을 생성하는 단계</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="42" hidden="0" customHeight="1">
       <x:c r="A80" s="50" t="n">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B80" s="50" t="str">
-        <x:v>가공도</x:v>
+        <x:v>제작·가공</x:v>
       </x:c>
       <x:c r="C80" s="50" t="str">
-        <x:v>치수·풍선</x:v>
+        <x:v>치수 디자인</x:v>
       </x:c>
       <x:c r="D80" s="51" t="str">
-        <x:v>치수·풍선 크기 종이 절대 정규화</x:v>
+        <x:v>작은 치수 텍스트 이동 시 치수선 길이 제어</x:v>
       </x:c>
       <x:c r="E80" s="50" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="F80" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="G80" s="50" t="str">
-        <x:v>△</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="H80" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>해당없음</x:v>
       </x:c>
       <x:c r="I80" s="50" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>API 요청 필요</x:v>
       </x:c>
       <x:c r="J80" s="51" t="str">
-        <x:v>모델 배율 비례 값을 캔버스 절대 크기 기준으로 교체 중</x:v>
+        <x:v>SetMeasureItemDistanceTextPos 사용 시 치수선이 양쪽으로 과도하게 연장</x:v>
       </x:c>
       <x:c r="K80" s="50" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>API 요청</x:v>
       </x:c>
       <x:c r="L80" s="50" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="M80" s="50" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="N80" s="55" t="n">
-        <x:v>46226</x:v>
-      </x:c>
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N80" s="55"/>
       <x:c r="O80" s="55"/>
       <x:c r="P80" s="55" t="n">
-        <x:v>46227</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="Q80" s="51" t="str">
-        <x:v>서로 다른 크기의 부재에서도 치수·풍선이 같은 종이 크기로 보이도록 정규화</x:v>
+        <x:v>버그가 아닌 낮은 우선순위 개선 요청이며 아직 API 요청을 전달하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="42" hidden="0" customHeight="1">
       <x:c r="A81" s="50" t="n">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="50" t="str">
-        <x:v>공통</x:v>
+        <x:v>제작·설치</x:v>
       </x:c>
       <x:c r="C81" s="50" t="str">
-        <x:v>자동화 UX</x:v>
+        <x:v>ISO 풍선 API</x:v>
       </x:c>
       <x:c r="D81" s="51" t="str">
-        <x:v>치수 추출·도면 출력 취소 응답성·진행률</x:v>
+        <x:v>연결부재 이름 풍선 상단·하단 방향 지정</x:v>
       </x:c>
       <x:c r="E81" s="50" t="str">
         <x:v>X</x:v>
@@ -6308,22 +6460,22 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G81" s="50" t="str">
-        <x:v>△</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="H81" s="50" t="str">
         <x:v>해당없음</x:v>
       </x:c>
       <x:c r="I81" s="50" t="str">
-        <x:v>개발 중</x:v>
+        <x:v>API 요청 필요</x:v>
       </x:c>
       <x:c r="J81" s="51" t="str">
-        <x:v>기본 취소는 있으나 BOM 반복 중 즉시 취소·진행률·대규모 대상 경고를 보강 중</x:v>
+        <x:v>SDK 자동 배치는 상·하·좌·우 네 방향을 임의 사용</x:v>
       </x:c>
       <x:c r="K81" s="50" t="str">
-        <x:v>앱 개발</x:v>
+        <x:v>API 요청</x:v>
       </x:c>
       <x:c r="L81" s="50" t="str">
-        <x:v>O</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="M81" s="50" t="str">
         <x:v>O</x:v>
@@ -6333,48 +6485,48 @@
       </x:c>
       <x:c r="O81" s="55"/>
       <x:c r="P81" s="55" t="n">
-        <x:v>46227</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="Q81" s="51" t="str">
-        <x:v>BOM 반복 구간에 취소 확인 지점과 진행률 갱신을 추가해야 함</x:v>
+        <x:v>연결부재 이름 풍선을 상단·하단 영역으로 제한하는 API 요청 필요</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="42" hidden="0" customHeight="1">
       <x:c r="A82" s="50" t="n">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B82" s="50" t="str">
-        <x:v>제작·가공</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C82" s="50" t="str">
-        <x:v>치수 디자인</x:v>
+        <x:v>형상</x:v>
       </x:c>
       <x:c r="D82" s="51" t="str">
-        <x:v>작은 치수 텍스트 이동 시 치수선 길이 제어</x:v>
+        <x:v>라운드 표시</x:v>
       </x:c>
       <x:c r="E82" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="F82" s="50" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="G82" s="50" t="str">
         <x:v>X</x:v>
       </x:c>
       <x:c r="H82" s="50" t="str">
-        <x:v>해당없음</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="I82" s="50" t="str">
-        <x:v>API 요청 필요</x:v>
+        <x:v>API 대기</x:v>
       </x:c>
       <x:c r="J82" s="51" t="str">
-        <x:v>SetMeasureItemDistanceTextPos 사용 시 치수선이 양쪽으로 과도하게 연장</x:v>
+        <x:v>라운드·필렛 판정 조건을 전달하고 형상 검출 API를 기다리는 상태</x:v>
       </x:c>
       <x:c r="K82" s="50" t="str">
-        <x:v>API 요청</x:v>
+        <x:v>API 대기</x:v>
       </x:c>
       <x:c r="L82" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="M82" s="50" t="str">
         <x:v>X</x:v>
@@ -6382,61 +6534,59 @@
       <x:c r="N82" s="55"/>
       <x:c r="O82" s="55"/>
       <x:c r="P82" s="55" t="n">
-        <x:v>46225</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q82" s="51" t="str">
-        <x:v>버그가 아닌 낮은 우선순위 개선 요청이며 아직 API 요청을 전달하지 않음</x:v>
+        <x:v>필터링 조건을 정리하면서 8월 API 수정·배포를 기다림</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" hidden="0" customHeight="1">
       <x:c r="A83" s="50" t="n">
-        <x:v>80</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B83" s="50" t="str">
-        <x:v>제작·설치</x:v>
+        <x:v>가공도</x:v>
       </x:c>
       <x:c r="C83" s="50" t="str">
-        <x:v>ISO 풍선 API</x:v>
+        <x:v>형상</x:v>
       </x:c>
       <x:c r="D83" s="51" t="str">
-        <x:v>연결부재 이름 풍선 상단·하단 방향 지정</x:v>
+        <x:v>모떼기(챔퍼) 표현</x:v>
       </x:c>
       <x:c r="E83" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="F83" s="50" t="str">
-        <x:v>○</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="G83" s="50" t="str">
         <x:v>X</x:v>
       </x:c>
       <x:c r="H83" s="50" t="str">
-        <x:v>해당없음</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="I83" s="50" t="str">
-        <x:v>API 요청 필요</x:v>
+        <x:v>API 대기</x:v>
       </x:c>
       <x:c r="J83" s="51" t="str">
-        <x:v>SDK 자동 배치는 상·하·좌·우 네 방향을 임의 사용</x:v>
+        <x:v>모떼기·챔퍼 판정 조건을 전달하고 형상 검출 API를 기다리는 상태</x:v>
       </x:c>
       <x:c r="K83" s="50" t="str">
-        <x:v>API 요청</x:v>
+        <x:v>API 대기</x:v>
       </x:c>
       <x:c r="L83" s="50" t="str">
-        <x:v>X</x:v>
+        <x:v>O</x:v>
       </x:c>
       <x:c r="M83" s="50" t="str">
-        <x:v>O</x:v>
-      </x:c>
-      <x:c r="N83" s="55" t="n">
-        <x:v>46226</x:v>
-      </x:c>
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N83" s="55"/>
       <x:c r="O83" s="55"/>
       <x:c r="P83" s="55" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q83" s="51" t="str">
-        <x:v>연결부재 이름 풍선을 상단·하단 영역으로 제한하는 API 요청 필요</x:v>
+        <x:v>필터링 조건을 정리하면서 8월 API 수정·배포를 기다림</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="42" hidden="0" customHeight="1">
@@ -6519,7 +6669,7 @@
         <x:v>API 대기</x:v>
       </x:c>
       <x:c r="J85" s="51" t="str">
-        <x:v>앱의 임시 각도 계산은 있으나 공식 API 결과로 교체 필요</x:v>
+        <x:v>공식 API를 기다리면서 앱의 Osnap 기반 접합 각도 구현을 병행</x:v>
       </x:c>
       <x:c r="K85" s="50" t="str">
         <x:v>API 대기</x:v>
@@ -6535,10 +6685,10 @@
       </x:c>
       <x:c r="O85" s="55"/>
       <x:c r="P85" s="55" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q85" s="51" t="str">
-        <x:v>부재 접합 각도 측정·표시 API의 8월 배포를 기다리는 상태</x:v>
+        <x:v>8월 API 배포를 기다리되 자체 구현을 예각·사선 부재로 계속 검증·보완</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="42" hidden="0" customHeight="1">
@@ -6703,7 +6853,7 @@
         <x:v>치수 API</x:v>
       </x:c>
       <x:c r="D89" s="51" t="str">
-        <x:v>ReferenceAxis+UserAxis 치수 문자 각도 보정</x:v>
+        <x:v>UserAxis 2D 치수 문자 각도 보정</x:v>
       </x:c>
       <x:c r="E89" s="50" t="str">
         <x:v>○</x:v>
@@ -6721,7 +6871,7 @@
         <x:v>API 대기</x:v>
       </x:c>
       <x:c r="J89" s="51" t="str">
-        <x:v>모델·치수선은 정렬되지만 숫자가 ±45°로 기울어짐</x:v>
+        <x:v>ReferenceAxis 정렬은 완료됐지만 치수 숫자만 ±45°로 기울어짐</x:v>
       </x:c>
       <x:c r="K89" s="50" t="str">
         <x:v>API 수정</x:v>
@@ -6737,10 +6887,10 @@
       </x:c>
       <x:c r="O89" s="55"/>
       <x:c r="P89" s="55" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="Q89" s="51" t="str">
-        <x:v>화면 수평 고정 또는 문자 회전각 제어 API 수정본 대기</x:v>
+        <x:v>참조축 정렬과 분리해 화면 수평 고정 또는 문자 회전각 제어 API만 대기</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="42" hidden="0" customHeight="1">
@@ -6883,22 +7033,22 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="I6:I90">
-    <x:cfRule type="expression" dxfId="50" priority="28">
+    <x:cfRule type="expression" dxfId="62" priority="28">
       <x:formula>$I6="완료"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="51" priority="29">
+    <x:cfRule type="expression" dxfId="63" priority="29">
       <x:formula>$I6="실기 검증 대기"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="52" priority="30">
+    <x:cfRule type="expression" dxfId="64" priority="30">
       <x:formula>OR($I6="부분 구현",$I6="개발 중")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="53" priority="31">
+    <x:cfRule type="expression" dxfId="65" priority="31">
       <x:formula>OR($I6="개발 필요",$I6="개발 대기")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="54" priority="32">
+    <x:cfRule type="expression" dxfId="66" priority="32">
       <x:formula>OR($I6="분석 필요",$I6="적용 제외")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="55" priority="33">
+    <x:cfRule type="expression" dxfId="67" priority="33">
       <x:formula>OR($I6="출력 불가",$I6="API 요청 필요",$I6="API 대기")</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -6927,7 +7077,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39b817ca4fc743f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9511c9bac9f41f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7634,25 +7784,25 @@
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="7" t="str">
-        <x:v>기울어진 부재 정렬</x:v>
+        <x:v>기울어진 부재 참조축 정렬</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
         <x:v>○</x:v>
       </x:c>
       <x:c r="C38" s="7" t="str">
-        <x:v>부분 구현</x:v>
+        <x:v>완료</x:v>
       </x:c>
       <x:c r="D38" s="7" t="str">
         <x:v>ORIENTATION UDA + ReferenceAxis 정렬 적용</x:v>
       </x:c>
       <x:c r="E38" s="7" t="str">
-        <x:v>치수 문자 각도·앵글 촬영 방향 기준 보강</x:v>
+        <x:v>UserAxis 문자 각도는 별도 API 대기</x:v>
       </x:c>
       <x:c r="F38" s="7" t="str">
-        <x:v>API/분석</x:v>
+        <x:v>API</x:v>
       </x:c>
       <x:c r="G38" s="7" t="str">
-        <x:v>기준축 정렬은 완료, 문자 각도와 앵글 카메라 규칙은 남음</x:v>
+        <x:v>참조축 정렬은 완료했고 치수 숫자 각도만 별도 항목으로 관리</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
